--- a/모찌런처_밸런스시트.xlsx
+++ b/모찌런처_밸런스시트.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="236">
   <si>
     <t>모찌 런처 — 밸런스 설정값</t>
   </si>
@@ -1110,6 +1110,57 @@
   </si>
   <si>
     <t>※ 목표 도달 판수는 tool/balance/pacing_sim.py 시뮬레이션(탐욕적 구매: 판 종료마다 씨앗 1개당 판당 씨앗 증가량이 가장 큰 업그레이드부터 반복 구매, 최선 항목이 부족하면 중단) 결과. 「진행 시뮬」 시트 참조.</t>
+  </si>
+  <si>
+    <t>체감 설정 (2.5D 샘플 HTML 기준)</t>
+  </si>
+  <si>
+    <t>샘플 발사 속도(100%)</t>
+  </si>
+  <si>
+    <t>feel_ref_v_px</t>
+  </si>
+  <si>
+    <t>px/s</t>
+  </si>
+  <si>
+    <t>모찌 런처 2.5D.html V100. Lv0 화면 움직임을 샘플과 같게 맞추는 기준</t>
+  </si>
+  <si>
+    <t>샘플 중력</t>
+  </si>
+  <si>
+    <t>feel_ref_g_px</t>
+  </si>
+  <si>
+    <t>px/s²</t>
+  </si>
+  <si>
+    <t>모찌 런처 2.5D.html GRAV</t>
+  </si>
+  <si>
+    <t>시뮬 시간 배율</t>
+  </si>
+  <si>
+    <t>sim_time_scale</t>
+  </si>
+  <si>
+    <t>배</t>
+  </si>
+  <si>
+    <t>계산식: 샘플g×v0 / (샘플v×g). 시뮬은 미터·실제 중력으로 계산하고(거리=공식 d), 이 배율로 빨리 재생해 샘플과 같은 체감 (ADR-012)</t>
+  </si>
+  <si>
+    <t>카메라 기본 배율</t>
+  </si>
+  <si>
+    <t>cam_base_px_per_m</t>
+  </si>
+  <si>
+    <t>px/m</t>
+  </si>
+  <si>
+    <t>계산식: 샘플v / (v0×시간배율). 가상 화면 높이 540 기준 Lv0 줌. 속도·고도에 따라 줌아웃</t>
   </si>
   <si>
     <r>
@@ -11112,7 +11163,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr defaultColWidth="8.67592592592593" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -11582,6 +11633,93 @@
       <c r="E26" s="15"/>
       <c r="F26" s="15"/>
       <c r="G26" s="15"/>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" t="s">
+        <v>71</v>
+      </c>
+      <c r="B28" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" t="s">
+        <v>31</v>
+      </c>
+      <c r="D28" t="s">
+        <v>32</v>
+      </c>
+      <c r="E28" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" t="s">
+        <v>72</v>
+      </c>
+      <c r="B29" t="s">
+        <v>73</v>
+      </c>
+      <c r="C29">
+        <v>1300</v>
+      </c>
+      <c r="D29" t="s">
+        <v>74</v>
+      </c>
+      <c r="E29" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" t="s">
+        <v>76</v>
+      </c>
+      <c r="B30" t="s">
+        <v>77</v>
+      </c>
+      <c r="C30">
+        <v>1400</v>
+      </c>
+      <c r="D30" t="s">
+        <v>78</v>
+      </c>
+      <c r="E30" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" t="s">
+        <v>80</v>
+      </c>
+      <c r="B31" t="s">
+        <v>81</v>
+      </c>
+      <c r="C31">
+        <f>ROUND(C30*C12/(C29*C13),4)</f>
+        <v>1.6484</v>
+      </c>
+      <c r="D31" t="s">
+        <v>82</v>
+      </c>
+      <c r="E31" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" t="s">
+        <v>84</v>
+      </c>
+      <c r="B32" t="s">
+        <v>85</v>
+      </c>
+      <c r="C32">
+        <f>ROUND(C29/(C12*C31),3)</f>
+        <v>52.576</v>
+      </c>
+      <c r="D32" t="s">
+        <v>86</v>
+      </c>
+      <c r="E32" t="s">
+        <v>87</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -11605,7 +11743,7 @@
   <sheetData>
     <row r="1" ht="17.4" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -11635,40 +11773,40 @@
     </row>
     <row r="3" ht="42.6" spans="1:12">
       <c r="A3" s="4" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>27</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -15668,7 +15806,7 @@
   <sheetData>
     <row r="1" ht="17.4" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -15690,7 +15828,7 @@
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="21" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="B2" s="15"/>
       <c r="C2" s="15"/>
@@ -15732,28 +15870,28 @@
     </row>
     <row r="4" ht="28.8" spans="1:18">
       <c r="A4" s="3" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>9</v>
@@ -16923,7 +17061,7 @@
       </c>
       <c r="N28" s="15"/>
       <c r="O28" s="12" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="P28" s="15"/>
       <c r="Q28" s="15"/>
@@ -16976,13 +17114,13 @@
         <v>53</v>
       </c>
       <c r="P29" s="23" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="Q29" s="23" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="R29" s="23" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
     </row>
     <row r="30" spans="1:18">
@@ -17413,7 +17551,7 @@
       </c>
       <c r="N37" s="15"/>
       <c r="O37" s="11" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="P37" s="15"/>
       <c r="Q37" s="15"/>
@@ -30256,7 +30394,7 @@
   <sheetData>
     <row r="1" ht="17.4" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -30270,7 +30408,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>31</v>
@@ -30279,145 +30417,145 @@
         <v>32</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="7" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="B4" s="6">
         <v>10000</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="5" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="B5" s="6">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="5" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="B6" s="6">
         <v>10</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="5" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="B7" s="6">
         <v>4</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="5" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="B8" s="6">
         <v>6</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="5" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="B9" s="16">
         <v>0.01</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="7" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="B10" s="16">
         <v>0.01</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="5" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="B11" s="6">
         <v>3</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="5" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="B12" s="16">
         <v>0.15</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="7" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="5" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="B13" s="6">
         <v>1380</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -30428,21 +30566,21 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="3" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="5" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="B16" s="17">
         <f>B4*B5*B6/1000</f>
@@ -30459,7 +30597,7 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="5" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="B17" s="17">
         <f>B4*(1-B9)*B7*B8/1000</f>
@@ -30476,7 +30614,7 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="7" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="B18" s="17">
         <f>B4*B10*B11*(1-B12)</f>
@@ -30493,7 +30631,7 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="12" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="B19" s="18">
         <f>SUM(B16:B18)</f>
@@ -30510,7 +30648,7 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="5" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="B20" s="19">
         <f>IF(B19&gt;0,(B16+B17)/B19,0)</f>
@@ -30521,7 +30659,7 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="7" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="B21" s="20">
         <f>IF(B4&gt;0,B19/B4,0)</f>
@@ -30538,7 +30676,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="B23" s="15"/>
       <c r="C23" s="15"/>
@@ -30566,29 +30704,29 @@
   <sheetData>
     <row r="1" ht="17.4" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="3" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="5" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="B4" s="6">
         <v>7</v>
@@ -30601,12 +30739,12 @@
         <v>210</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="5" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="B5" s="6">
         <v>7</v>
@@ -30622,7 +30760,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="7" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="B6" s="6">
         <v>1</v>
@@ -30635,12 +30773,12 @@
         <v>100</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="5" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="B7" s="6">
         <v>3</v>
@@ -30653,12 +30791,12 @@
         <v>60</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="5" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="B8" s="6">
         <v>5</v>
@@ -30671,12 +30809,12 @@
         <v>25</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="12" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="D9" s="12">
         <f>SUM(D4:D8)</f>
@@ -30685,22 +30823,22 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="3" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="5" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="B12" s="6">
         <v>100</v>
@@ -30710,12 +30848,12 @@
         <v>5.4</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="5" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="B13" s="6">
         <v>300</v>
@@ -30728,7 +30866,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="5" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="B14" s="6">
         <v>20</v>
@@ -30741,7 +30879,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="5" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="B15" s="6">
         <v>150</v>
@@ -30754,24 +30892,24 @@
     </row>
     <row r="17" ht="28.2" spans="1:5">
       <c r="A17" s="3" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="B18" s="13">
         <v>1200</v>
@@ -30790,7 +30928,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="B19" s="13">
         <v>5900</v>
@@ -30809,7 +30947,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="B20" s="13">
         <v>29000</v>
@@ -30828,7 +30966,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="B21" s="13">
         <v>5900</v>
@@ -30847,7 +30985,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="B22" s="13">
         <v>2500</v>
@@ -30866,7 +31004,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="B23" s="13">
         <v>4400</v>
@@ -30885,7 +31023,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -30911,17 +31049,17 @@
   <sheetData>
     <row r="1" ht="17.4" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4" ht="28.2" spans="1:8">
       <c r="A4" s="3" t="s">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>31</v>
@@ -30932,88 +31070,88 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="5" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="B5" s="6">
         <v>0.2</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>177</v>
+        <v>194</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="5" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="B6" s="6">
         <v>0.15</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="5" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="B7" s="6">
         <v>0.1</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="5" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="B8" s="6">
         <v>8</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="5" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="B9" s="6">
         <v>2</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="1:8">
       <c r="A11" s="3" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="5" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="B12" s="8">
         <v>346</v>
@@ -31043,7 +31181,7 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="5" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="B13" s="8">
         <v>1919</v>
@@ -31073,7 +31211,7 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="5" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="B14" s="8">
         <v>7903</v>
@@ -31103,7 +31241,7 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="5" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="B15" s="8">
         <v>24394</v>
@@ -31133,7 +31271,7 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="5" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="B16" s="8">
         <v>84051</v>
@@ -31163,12 +31301,12 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="2" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="11" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -31186,38 +31324,38 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="B4" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="C4" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="D4" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="E4" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="F4" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="G4" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="H4" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -31323,7 +31461,7 @@
         <v>500</v>
       </c>
       <c r="D9" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="E9">
         <v>13</v>
@@ -31441,7 +31579,7 @@
         <v>2000</v>
       </c>
       <c r="D14" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="E14">
         <v>20</v>
@@ -31559,7 +31697,7 @@
         <v>6000</v>
       </c>
       <c r="D19" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="E19">
         <v>29</v>
@@ -31677,7 +31815,7 @@
         <v>15000</v>
       </c>
       <c r="D24" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="E24">
         <v>45</v>
@@ -31795,7 +31933,7 @@
         <v>40000</v>
       </c>
       <c r="D29" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="E29">
         <v>113</v>
@@ -31812,30 +31950,30 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="B32" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="C32">
         <v>1.3</v>
       </c>
       <c r="D32" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="B34" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="C34" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="D34" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -31843,7 +31981,7 @@
         <v>2</v>
       </c>
       <c r="B35" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="C35">
         <v>8</v>
@@ -31854,7 +31992,7 @@
         <v>3</v>
       </c>
       <c r="B36" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="C36">
         <v>20</v>
@@ -31865,7 +32003,7 @@
         <v>4</v>
       </c>
       <c r="B37" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="C37">
         <v>32</v>
@@ -31876,7 +32014,7 @@
         <v>5</v>
       </c>
       <c r="B38" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="C38">
         <v>45</v>
@@ -31887,7 +32025,7 @@
         <v>6</v>
       </c>
       <c r="B39" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="C39">
         <v>60</v>

--- a/모찌런처_밸런스시트.xlsx
+++ b/모찌런처_밸런스시트.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="290">
   <si>
     <t>모찌 런처 — 밸런스 설정값</t>
   </si>
@@ -1161,6 +1161,168 @@
   </si>
   <si>
     <t>계산식: 샘플v / (v0×시간배율). 가상 화면 높이 540 기준 Lv0 줌. 속도·고도에 따라 줌아웃</t>
+  </si>
+  <si>
+    <t>정확도 게이지·당기기 (GDD §2)</t>
+  </si>
+  <si>
+    <t>최대 힘</t>
+  </si>
+  <si>
+    <t>gauge_max_power</t>
+  </si>
+  <si>
+    <t>힘 0~110%</t>
+  </si>
+  <si>
+    <t>바늘 기본 속도</t>
+  </si>
+  <si>
+    <t>gauge_speed_base</t>
+  </si>
+  <si>
+    <t>트랙/초</t>
+  </si>
+  <si>
+    <t>p≤1: 0.45 + 1.35p</t>
+  </si>
+  <si>
+    <t>바늘 속도 계수</t>
+  </si>
+  <si>
+    <t>gauge_speed_k</t>
+  </si>
+  <si>
+    <t>p≤1 기울기</t>
+  </si>
+  <si>
+    <t>과충전 가속</t>
+  </si>
+  <si>
+    <t>gauge_over_k</t>
+  </si>
+  <si>
+    <t>p&gt;1: 1.8 × (1 + 9(p−1))</t>
+  </si>
+  <si>
+    <t>PERFECT 폭</t>
+  </si>
+  <si>
+    <t>gauge_zone_width</t>
+  </si>
+  <si>
+    <t>off</t>
+  </si>
+  <si>
+    <t>가운데에서 벗어난 정도 off ≤ 0.1 (트랙 0.45~0.55)</t>
+  </si>
+  <si>
+    <t>GREAT 경계</t>
+  </si>
+  <si>
+    <t>gauge_great_off</t>
+  </si>
+  <si>
+    <t>off ≤ 0.3 (트랙 0.35~0.65)</t>
+  </si>
+  <si>
+    <t>GOOD 경계</t>
+  </si>
+  <si>
+    <t>gauge_good_off</t>
+  </si>
+  <si>
+    <t>off ≤ 0.6 (트랙 0.20~0.80), 나머지 아쉬워요</t>
+  </si>
+  <si>
+    <t>PERFECT 배율</t>
+  </si>
+  <si>
+    <t>gauge_perfect_mult</t>
+  </si>
+  <si>
+    <t>GREAT 최소 배율</t>
+  </si>
+  <si>
+    <t>gauge_great_mult_min</t>
+  </si>
+  <si>
+    <t>구간 바깥 경계 값. 안쪽 경계로 갈수록 최대까지 선형 보간</t>
+  </si>
+  <si>
+    <t>GREAT 최대 배율</t>
+  </si>
+  <si>
+    <t>gauge_great_mult_max</t>
+  </si>
+  <si>
+    <t>GDD 표 ×1.03~1.13 (ADR-013, 샘플은 1.097 까지만)</t>
+  </si>
+  <si>
+    <t>GOOD 최소 배율</t>
+  </si>
+  <si>
+    <t>gauge_good_mult_min</t>
+  </si>
+  <si>
+    <t>GOOD 최대 배율</t>
+  </si>
+  <si>
+    <t>gauge_good_mult_max</t>
+  </si>
+  <si>
+    <t>아쉬워요 최소 배율</t>
+  </si>
+  <si>
+    <t>gauge_miss_mult_min</t>
+  </si>
+  <si>
+    <t>아쉬워요 최대 배율</t>
+  </si>
+  <si>
+    <t>gauge_miss_mult_max</t>
+  </si>
+  <si>
+    <t>배율 → 속도 지수</t>
+  </si>
+  <si>
+    <t>gauge_speed_exponent</t>
+  </si>
+  <si>
+    <t>발사 속도 × (힘×배율)^지수. 0.5 = 힘×배율이 거리에 그대로 곱해짐(GDD "최대 거리 ×1.27"). 1 = 샘플처럼 속도에 곱함(거리는 제곱)</t>
+  </si>
+  <si>
+    <t>최대 당김 거리</t>
+  </si>
+  <si>
+    <t>pull_max_px</t>
+  </si>
+  <si>
+    <t>가상 px</t>
+  </si>
+  <si>
+    <t>샘플 MAXPULL. 이 거리에서 힘 110%</t>
+  </si>
+  <si>
+    <t>최소 발사 힘</t>
+  </si>
+  <si>
+    <t>pull_min_power</t>
+  </si>
+  <si>
+    <t>이보다 약하게 놓으면 발사 취소 (샘플과 같음)</t>
+  </si>
+  <si>
+    <t>최대 발사 각</t>
+  </si>
+  <si>
+    <t>launch_angle_max_deg</t>
+  </si>
+  <si>
+    <t>°</t>
+  </si>
+  <si>
+    <t>뒤로만 날아가지 않게 0°~최대 각으로 제한</t>
   </si>
   <si>
     <r>
@@ -11163,7 +11325,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr defaultColWidth="8.67592592592593" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -11719,6 +11881,314 @@
       </c>
       <c r="E32" t="s">
         <v>87</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" t="s">
+        <v>88</v>
+      </c>
+      <c r="B34" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" t="s">
+        <v>31</v>
+      </c>
+      <c r="D34" t="s">
+        <v>32</v>
+      </c>
+      <c r="E34" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
+        <v>89</v>
+      </c>
+      <c r="B35" t="s">
+        <v>90</v>
+      </c>
+      <c r="C35">
+        <v>1.1</v>
+      </c>
+      <c r="D35" t="s">
+        <v>82</v>
+      </c>
+      <c r="E35" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
+        <v>92</v>
+      </c>
+      <c r="B36" t="s">
+        <v>93</v>
+      </c>
+      <c r="C36">
+        <v>0.45</v>
+      </c>
+      <c r="D36" t="s">
+        <v>94</v>
+      </c>
+      <c r="E36" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" t="s">
+        <v>96</v>
+      </c>
+      <c r="B37" t="s">
+        <v>97</v>
+      </c>
+      <c r="C37">
+        <v>1.35</v>
+      </c>
+      <c r="D37" t="s">
+        <v>94</v>
+      </c>
+      <c r="E37" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" t="s">
+        <v>99</v>
+      </c>
+      <c r="B38" t="s">
+        <v>100</v>
+      </c>
+      <c r="C38">
+        <v>9</v>
+      </c>
+      <c r="D38" t="s">
+        <v>82</v>
+      </c>
+      <c r="E38" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" t="s">
+        <v>102</v>
+      </c>
+      <c r="B39" t="s">
+        <v>103</v>
+      </c>
+      <c r="C39">
+        <v>0.1</v>
+      </c>
+      <c r="D39" t="s">
+        <v>104</v>
+      </c>
+      <c r="E39" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" t="s">
+        <v>106</v>
+      </c>
+      <c r="B40" t="s">
+        <v>107</v>
+      </c>
+      <c r="C40">
+        <v>0.3</v>
+      </c>
+      <c r="D40" t="s">
+        <v>104</v>
+      </c>
+      <c r="E40" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" t="s">
+        <v>109</v>
+      </c>
+      <c r="B41" t="s">
+        <v>110</v>
+      </c>
+      <c r="C41">
+        <v>0.6</v>
+      </c>
+      <c r="D41" t="s">
+        <v>104</v>
+      </c>
+      <c r="E41" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" t="s">
+        <v>112</v>
+      </c>
+      <c r="B42" t="s">
+        <v>113</v>
+      </c>
+      <c r="C42">
+        <v>1.15</v>
+      </c>
+      <c r="D42" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" t="s">
+        <v>114</v>
+      </c>
+      <c r="B43" t="s">
+        <v>115</v>
+      </c>
+      <c r="C43">
+        <v>1.03</v>
+      </c>
+      <c r="D43" t="s">
+        <v>82</v>
+      </c>
+      <c r="E43" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" t="s">
+        <v>117</v>
+      </c>
+      <c r="B44" t="s">
+        <v>118</v>
+      </c>
+      <c r="C44">
+        <v>1.13</v>
+      </c>
+      <c r="D44" t="s">
+        <v>82</v>
+      </c>
+      <c r="E44" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" t="s">
+        <v>120</v>
+      </c>
+      <c r="B45" t="s">
+        <v>121</v>
+      </c>
+      <c r="C45">
+        <v>0.95</v>
+      </c>
+      <c r="D45" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" t="s">
+        <v>122</v>
+      </c>
+      <c r="B46" t="s">
+        <v>123</v>
+      </c>
+      <c r="C46">
+        <v>1.03</v>
+      </c>
+      <c r="D46" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" t="s">
+        <v>124</v>
+      </c>
+      <c r="B47" t="s">
+        <v>125</v>
+      </c>
+      <c r="C47">
+        <v>0.8</v>
+      </c>
+      <c r="D47" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" t="s">
+        <v>126</v>
+      </c>
+      <c r="B48" t="s">
+        <v>127</v>
+      </c>
+      <c r="C48">
+        <v>0.95</v>
+      </c>
+      <c r="D48" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" t="s">
+        <v>128</v>
+      </c>
+      <c r="B49" t="s">
+        <v>129</v>
+      </c>
+      <c r="C49">
+        <v>0.5</v>
+      </c>
+      <c r="D49" t="s">
+        <v>19</v>
+      </c>
+      <c r="E49" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" t="s">
+        <v>131</v>
+      </c>
+      <c r="B50" t="s">
+        <v>132</v>
+      </c>
+      <c r="C50">
+        <v>150</v>
+      </c>
+      <c r="D50" t="s">
+        <v>133</v>
+      </c>
+      <c r="E50" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" t="s">
+        <v>135</v>
+      </c>
+      <c r="B51" t="s">
+        <v>136</v>
+      </c>
+      <c r="C51">
+        <v>0.08</v>
+      </c>
+      <c r="D51" t="s">
+        <v>82</v>
+      </c>
+      <c r="E51" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" t="s">
+        <v>138</v>
+      </c>
+      <c r="B52" t="s">
+        <v>139</v>
+      </c>
+      <c r="C52">
+        <v>85</v>
+      </c>
+      <c r="D52" t="s">
+        <v>140</v>
+      </c>
+      <c r="E52" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -11743,7 +12213,7 @@
   <sheetData>
     <row r="1" ht="17.4" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>88</v>
+        <v>142</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -11773,40 +12243,40 @@
     </row>
     <row r="3" ht="42.6" spans="1:12">
       <c r="A3" s="4" t="s">
-        <v>89</v>
+        <v>143</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>90</v>
+        <v>144</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>91</v>
+        <v>145</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>92</v>
+        <v>146</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>93</v>
+        <v>147</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>94</v>
+        <v>148</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>95</v>
+        <v>149</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>96</v>
+        <v>150</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>97</v>
+        <v>151</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>98</v>
+        <v>152</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>27</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>99</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -15806,7 +16276,7 @@
   <sheetData>
     <row r="1" ht="17.4" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>100</v>
+        <v>154</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -15828,7 +16298,7 @@
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="21" t="s">
-        <v>101</v>
+        <v>155</v>
       </c>
       <c r="B2" s="15"/>
       <c r="C2" s="15"/>
@@ -15870,28 +16340,28 @@
     </row>
     <row r="4" ht="28.8" spans="1:18">
       <c r="A4" s="3" t="s">
-        <v>102</v>
+        <v>156</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>103</v>
+        <v>157</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>105</v>
+        <v>159</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>106</v>
+        <v>160</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>107</v>
+        <v>161</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>108</v>
+        <v>162</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>109</v>
+        <v>163</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>9</v>
@@ -17061,7 +17531,7 @@
       </c>
       <c r="N28" s="15"/>
       <c r="O28" s="12" t="s">
-        <v>110</v>
+        <v>164</v>
       </c>
       <c r="P28" s="15"/>
       <c r="Q28" s="15"/>
@@ -17114,13 +17584,13 @@
         <v>53</v>
       </c>
       <c r="P29" s="23" t="s">
-        <v>111</v>
+        <v>165</v>
       </c>
       <c r="Q29" s="23" t="s">
-        <v>112</v>
+        <v>166</v>
       </c>
       <c r="R29" s="23" t="s">
-        <v>113</v>
+        <v>167</v>
       </c>
     </row>
     <row r="30" spans="1:18">
@@ -17551,7 +18021,7 @@
       </c>
       <c r="N37" s="15"/>
       <c r="O37" s="11" t="s">
-        <v>114</v>
+        <v>168</v>
       </c>
       <c r="P37" s="15"/>
       <c r="Q37" s="15"/>
@@ -30394,7 +30864,7 @@
   <sheetData>
     <row r="1" ht="17.4" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>115</v>
+        <v>169</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -30408,7 +30878,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>116</v>
+        <v>170</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>31</v>
@@ -30417,145 +30887,145 @@
         <v>32</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="7" t="s">
-        <v>118</v>
+        <v>172</v>
       </c>
       <c r="B4" s="6">
         <v>10000</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>119</v>
+        <v>173</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>120</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="5" t="s">
-        <v>121</v>
+        <v>175</v>
       </c>
       <c r="B5" s="6">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>122</v>
+        <v>176</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>123</v>
+        <v>177</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="5" t="s">
-        <v>124</v>
+        <v>178</v>
       </c>
       <c r="B6" s="6">
         <v>10</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>125</v>
+        <v>179</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>126</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="5" t="s">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="B7" s="6">
         <v>4</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>122</v>
+        <v>176</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>128</v>
+        <v>182</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="5" t="s">
-        <v>129</v>
+        <v>183</v>
       </c>
       <c r="B8" s="6">
         <v>6</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>125</v>
+        <v>179</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>130</v>
+        <v>184</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="5" t="s">
-        <v>131</v>
+        <v>185</v>
       </c>
       <c r="B9" s="16">
         <v>0.01</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>132</v>
+        <v>186</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>130</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="7" t="s">
-        <v>133</v>
+        <v>187</v>
       </c>
       <c r="B10" s="16">
         <v>0.01</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>134</v>
+        <v>188</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>135</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="5" t="s">
-        <v>136</v>
+        <v>190</v>
       </c>
       <c r="B11" s="6">
         <v>3</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>125</v>
+        <v>179</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>137</v>
+        <v>191</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="5" t="s">
-        <v>138</v>
+        <v>192</v>
       </c>
       <c r="B12" s="16">
         <v>0.15</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="7" t="s">
-        <v>139</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="5" t="s">
-        <v>140</v>
+        <v>194</v>
       </c>
       <c r="B13" s="6">
         <v>1380</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>141</v>
+        <v>195</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>142</v>
+        <v>196</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -30566,21 +31036,21 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="3" t="s">
-        <v>143</v>
+        <v>197</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>144</v>
+        <v>198</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>145</v>
+        <v>199</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>146</v>
+        <v>200</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="5" t="s">
-        <v>147</v>
+        <v>201</v>
       </c>
       <c r="B16" s="17">
         <f>B4*B5*B6/1000</f>
@@ -30597,7 +31067,7 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="5" t="s">
-        <v>148</v>
+        <v>202</v>
       </c>
       <c r="B17" s="17">
         <f>B4*(1-B9)*B7*B8/1000</f>
@@ -30614,7 +31084,7 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="7" t="s">
-        <v>149</v>
+        <v>203</v>
       </c>
       <c r="B18" s="17">
         <f>B4*B10*B11*(1-B12)</f>
@@ -30631,7 +31101,7 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="12" t="s">
-        <v>150</v>
+        <v>204</v>
       </c>
       <c r="B19" s="18">
         <f>SUM(B16:B18)</f>
@@ -30648,7 +31118,7 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="5" t="s">
-        <v>151</v>
+        <v>205</v>
       </c>
       <c r="B20" s="19">
         <f>IF(B19&gt;0,(B16+B17)/B19,0)</f>
@@ -30659,7 +31129,7 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="7" t="s">
-        <v>152</v>
+        <v>206</v>
       </c>
       <c r="B21" s="20">
         <f>IF(B4&gt;0,B19/B4,0)</f>
@@ -30676,7 +31146,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>153</v>
+        <v>207</v>
       </c>
       <c r="B23" s="15"/>
       <c r="C23" s="15"/>
@@ -30704,29 +31174,29 @@
   <sheetData>
     <row r="1" ht="17.4" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>154</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="3" t="s">
-        <v>155</v>
+        <v>209</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>156</v>
+        <v>210</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>157</v>
+        <v>211</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>158</v>
+        <v>212</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>159</v>
+        <v>213</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="5" t="s">
-        <v>160</v>
+        <v>214</v>
       </c>
       <c r="B4" s="6">
         <v>7</v>
@@ -30739,12 +31209,12 @@
         <v>210</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>161</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="5" t="s">
-        <v>162</v>
+        <v>216</v>
       </c>
       <c r="B5" s="6">
         <v>7</v>
@@ -30760,7 +31230,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="7" t="s">
-        <v>163</v>
+        <v>217</v>
       </c>
       <c r="B6" s="6">
         <v>1</v>
@@ -30773,12 +31243,12 @@
         <v>100</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>164</v>
+        <v>218</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="5" t="s">
-        <v>165</v>
+        <v>219</v>
       </c>
       <c r="B7" s="6">
         <v>3</v>
@@ -30791,12 +31261,12 @@
         <v>60</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>166</v>
+        <v>220</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="5" t="s">
-        <v>167</v>
+        <v>221</v>
       </c>
       <c r="B8" s="6">
         <v>5</v>
@@ -30809,12 +31279,12 @@
         <v>25</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>168</v>
+        <v>222</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="12" t="s">
-        <v>169</v>
+        <v>223</v>
       </c>
       <c r="D9" s="12">
         <f>SUM(D4:D8)</f>
@@ -30823,22 +31293,22 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="3" t="s">
-        <v>170</v>
+        <v>224</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>171</v>
+        <v>225</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3" t="s">
-        <v>172</v>
+        <v>226</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>159</v>
+        <v>213</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="5" t="s">
-        <v>173</v>
+        <v>227</v>
       </c>
       <c r="B12" s="6">
         <v>100</v>
@@ -30848,12 +31318,12 @@
         <v>5.4</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>174</v>
+        <v>228</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="5" t="s">
-        <v>175</v>
+        <v>229</v>
       </c>
       <c r="B13" s="6">
         <v>300</v>
@@ -30866,7 +31336,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="5" t="s">
-        <v>176</v>
+        <v>230</v>
       </c>
       <c r="B14" s="6">
         <v>20</v>
@@ -30879,7 +31349,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="5" t="s">
-        <v>177</v>
+        <v>231</v>
       </c>
       <c r="B15" s="6">
         <v>150</v>
@@ -30892,24 +31362,24 @@
     </row>
     <row r="17" ht="28.2" spans="1:5">
       <c r="A17" s="3" t="s">
-        <v>178</v>
+        <v>232</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>179</v>
+        <v>233</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>180</v>
+        <v>234</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>181</v>
+        <v>235</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>182</v>
+        <v>236</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>183</v>
+        <v>237</v>
       </c>
       <c r="B18" s="13">
         <v>1200</v>
@@ -30928,7 +31398,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>184</v>
+        <v>238</v>
       </c>
       <c r="B19" s="13">
         <v>5900</v>
@@ -30947,7 +31417,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>185</v>
+        <v>239</v>
       </c>
       <c r="B20" s="13">
         <v>29000</v>
@@ -30966,7 +31436,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>186</v>
+        <v>240</v>
       </c>
       <c r="B21" s="13">
         <v>5900</v>
@@ -30985,7 +31455,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>187</v>
+        <v>241</v>
       </c>
       <c r="B22" s="13">
         <v>2500</v>
@@ -31004,7 +31474,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>188</v>
+        <v>242</v>
       </c>
       <c r="B23" s="13">
         <v>4400</v>
@@ -31023,7 +31493,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2" t="s">
-        <v>189</v>
+        <v>243</v>
       </c>
     </row>
   </sheetData>
@@ -31049,17 +31519,17 @@
   <sheetData>
     <row r="1" ht="17.4" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>190</v>
+        <v>244</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>191</v>
+        <v>245</v>
       </c>
     </row>
     <row r="4" ht="28.2" spans="1:8">
       <c r="A4" s="3" t="s">
-        <v>192</v>
+        <v>246</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>31</v>
@@ -31070,88 +31540,88 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="5" t="s">
-        <v>193</v>
+        <v>247</v>
       </c>
       <c r="B5" s="6">
         <v>0.2</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>194</v>
+        <v>248</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="5" t="s">
-        <v>195</v>
+        <v>249</v>
       </c>
       <c r="B6" s="6">
         <v>0.15</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>196</v>
+        <v>250</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="5" t="s">
-        <v>197</v>
+        <v>251</v>
       </c>
       <c r="B7" s="6">
         <v>0.1</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>198</v>
+        <v>252</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="5" t="s">
-        <v>199</v>
+        <v>253</v>
       </c>
       <c r="B8" s="6">
         <v>8</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>200</v>
+        <v>254</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="5" t="s">
-        <v>201</v>
+        <v>255</v>
       </c>
       <c r="B9" s="6">
         <v>2</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>202</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="1:8">
       <c r="A11" s="3" t="s">
-        <v>203</v>
+        <v>257</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>204</v>
+        <v>258</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>205</v>
+        <v>259</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>206</v>
+        <v>260</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>207</v>
+        <v>261</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>208</v>
+        <v>262</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>209</v>
+        <v>263</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>210</v>
+        <v>264</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="5" t="s">
-        <v>211</v>
+        <v>265</v>
       </c>
       <c r="B12" s="8">
         <v>346</v>
@@ -31181,7 +31651,7 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="5" t="s">
-        <v>212</v>
+        <v>266</v>
       </c>
       <c r="B13" s="8">
         <v>1919</v>
@@ -31211,7 +31681,7 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="5" t="s">
-        <v>213</v>
+        <v>267</v>
       </c>
       <c r="B14" s="8">
         <v>7903</v>
@@ -31241,7 +31711,7 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="5" t="s">
-        <v>214</v>
+        <v>268</v>
       </c>
       <c r="B15" s="8">
         <v>24394</v>
@@ -31271,7 +31741,7 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="5" t="s">
-        <v>215</v>
+        <v>269</v>
       </c>
       <c r="B16" s="8">
         <v>84051</v>
@@ -31301,12 +31771,12 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="2" t="s">
-        <v>216</v>
+        <v>270</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="11" t="s">
-        <v>217</v>
+        <v>271</v>
       </c>
     </row>
   </sheetData>
@@ -31324,38 +31794,38 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>218</v>
+        <v>272</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>219</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>220</v>
+        <v>274</v>
       </c>
       <c r="B4" t="s">
-        <v>221</v>
+        <v>275</v>
       </c>
       <c r="C4" t="s">
-        <v>222</v>
+        <v>276</v>
       </c>
       <c r="D4" t="s">
-        <v>223</v>
+        <v>277</v>
       </c>
       <c r="E4" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="F4" t="s">
-        <v>225</v>
+        <v>279</v>
       </c>
       <c r="G4" t="s">
-        <v>226</v>
+        <v>280</v>
       </c>
       <c r="H4" t="s">
-        <v>227</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -31461,7 +31931,7 @@
         <v>500</v>
       </c>
       <c r="D9" t="s">
-        <v>223</v>
+        <v>277</v>
       </c>
       <c r="E9">
         <v>13</v>
@@ -31579,7 +32049,7 @@
         <v>2000</v>
       </c>
       <c r="D14" t="s">
-        <v>223</v>
+        <v>277</v>
       </c>
       <c r="E14">
         <v>20</v>
@@ -31697,7 +32167,7 @@
         <v>6000</v>
       </c>
       <c r="D19" t="s">
-        <v>223</v>
+        <v>277</v>
       </c>
       <c r="E19">
         <v>29</v>
@@ -31815,7 +32285,7 @@
         <v>15000</v>
       </c>
       <c r="D24" t="s">
-        <v>223</v>
+        <v>277</v>
       </c>
       <c r="E24">
         <v>45</v>
@@ -31933,7 +32403,7 @@
         <v>40000</v>
       </c>
       <c r="D29" t="s">
-        <v>223</v>
+        <v>277</v>
       </c>
       <c r="E29">
         <v>113</v>
@@ -31950,30 +32420,30 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" t="s">
-        <v>228</v>
+        <v>282</v>
       </c>
       <c r="B32" t="s">
-        <v>229</v>
+        <v>283</v>
       </c>
       <c r="C32">
         <v>1.3</v>
       </c>
       <c r="D32" t="s">
-        <v>230</v>
+        <v>284</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>231</v>
+        <v>285</v>
       </c>
       <c r="B34" t="s">
-        <v>232</v>
+        <v>286</v>
       </c>
       <c r="C34" t="s">
-        <v>233</v>
+        <v>287</v>
       </c>
       <c r="D34" t="s">
-        <v>234</v>
+        <v>288</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -31981,7 +32451,7 @@
         <v>2</v>
       </c>
       <c r="B35" t="s">
-        <v>235</v>
+        <v>289</v>
       </c>
       <c r="C35">
         <v>8</v>
@@ -31992,7 +32462,7 @@
         <v>3</v>
       </c>
       <c r="B36" t="s">
-        <v>235</v>
+        <v>289</v>
       </c>
       <c r="C36">
         <v>20</v>
@@ -32003,7 +32473,7 @@
         <v>4</v>
       </c>
       <c r="B37" t="s">
-        <v>235</v>
+        <v>289</v>
       </c>
       <c r="C37">
         <v>32</v>
@@ -32014,7 +32484,7 @@
         <v>5</v>
       </c>
       <c r="B38" t="s">
-        <v>235</v>
+        <v>289</v>
       </c>
       <c r="C38">
         <v>45</v>
@@ -32025,7 +32495,7 @@
         <v>6</v>
       </c>
       <c r="B39" t="s">
-        <v>235</v>
+        <v>289</v>
       </c>
       <c r="C39">
         <v>60</v>

--- a/모찌런처_밸런스시트.xlsx
+++ b/모찌런처_밸런스시트.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="326">
   <si>
     <t>모찌 런처 — 밸런스 설정값</t>
   </si>
@@ -1323,6 +1323,114 @@
   </si>
   <si>
     <t>뒤로만 날아가지 않게 0°~최대 각으로 제한</t>
+  </si>
+  <si>
+    <t>비행 조작 (GDD §2 비행 중 조작 3종)</t>
+  </si>
+  <si>
+    <t>부스터 연료</t>
+  </si>
+  <si>
+    <t>boost_fuel_sec</t>
+  </si>
+  <si>
+    <t>2.5D 샘플 fuel 1.5. 연료 = 공식 부스터 거리(20·Lv^1.3 × 바운스 배율)를 이 시간 동안 나눠 씀. 공중에서 다 쓰면 공식 거리와 같음</t>
+  </si>
+  <si>
+    <t>부스터 1탭 분사</t>
+  </si>
+  <si>
+    <t>boost_tap_sec</t>
+  </si>
+  <si>
+    <t>탭 한 번에 쓰는 연료 (1.5초 = 5탭)</t>
+  </si>
+  <si>
+    <t>볼 부풀리기 활공비</t>
+  </si>
+  <si>
+    <t>inflate_glide_ratio</t>
+  </si>
+  <si>
+    <t>낙하/수평</t>
+  </si>
+  <si>
+    <t>부풀린 동안 낙하 속도 ≤ 수평 속도 × 이 값 (낙하산 활공)</t>
+  </si>
+  <si>
+    <t>볼 부풀리기 감속</t>
+  </si>
+  <si>
+    <t>inflate_drag_per_sec</t>
+  </si>
+  <si>
+    <t>1/초</t>
+  </si>
+  <si>
+    <t>부풀린 동안 수평 속도 감소율 (멀리 vs 빠르게)</t>
+  </si>
+  <si>
+    <t>급강하 속도비</t>
+  </si>
+  <si>
+    <t>dive_speed_ratio</t>
+  </si>
+  <si>
+    <t>급강하 시 낙하 속도 = 수평 속도 × 이 값 이상</t>
+  </si>
+  <si>
+    <t>급강하 바운스 배율</t>
+  </si>
+  <si>
+    <t>dive_bounce_mult</t>
+  </si>
+  <si>
+    <t>급강하로 바운스 오브젝트를 맞히면 튀는 속도 배율 (P5)</t>
+  </si>
+  <si>
+    <t>급강하 퍼펙트 창</t>
+  </si>
+  <si>
+    <t>dive_perfect_window_sec</t>
+  </si>
+  <si>
+    <t>급강하 시작 후 이 시간 안에 맞히면 퍼펙트 (P5)</t>
+  </si>
+  <si>
+    <t>급강하 퍼펙트 배율</t>
+  </si>
+  <si>
+    <t>dive_perfect_mult</t>
+  </si>
+  <si>
+    <t>퍼펙트 보너스 튀는 속도 배율 (P5)</t>
+  </si>
+  <si>
+    <t>홀드 판정 시간</t>
+  </si>
+  <si>
+    <t>gesture_hold_sec</t>
+  </si>
+  <si>
+    <t>이보다 오래 누르면 볼 부풀리기, 짧게 떼면 부스터 탭</t>
+  </si>
+  <si>
+    <t>스와이프 거리</t>
+  </si>
+  <si>
+    <t>gesture_swipe_px</t>
+  </si>
+  <si>
+    <t>아래로 이만큼 쓸면 급강하</t>
+  </si>
+  <si>
+    <t>스와이프 시간</t>
+  </si>
+  <si>
+    <t>gesture_swipe_max_sec</t>
+  </si>
+  <si>
+    <t>이 시간 안에 쓸어야 스와이프</t>
   </si>
   <si>
     <r>
@@ -4421,14 +4529,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="14"/>
+      <i/>
+      <sz val="11"/>
       <name val="Arial"/>
       <charset val="1"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
+      <b/>
+      <sz val="14"/>
       <name val="Arial"/>
       <charset val="1"/>
     </font>
@@ -11325,7 +11433,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr defaultColWidth="8.67592592592593" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -12189,6 +12297,210 @@
       </c>
       <c r="E52" t="s">
         <v>141</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" t="s">
+        <v>142</v>
+      </c>
+      <c r="B54" t="s">
+        <v>30</v>
+      </c>
+      <c r="C54" t="s">
+        <v>31</v>
+      </c>
+      <c r="D54" t="s">
+        <v>32</v>
+      </c>
+      <c r="E54" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" t="s">
+        <v>143</v>
+      </c>
+      <c r="B55" t="s">
+        <v>144</v>
+      </c>
+      <c r="C55">
+        <v>1.5</v>
+      </c>
+      <c r="D55" t="s">
+        <v>51</v>
+      </c>
+      <c r="E55" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" t="s">
+        <v>146</v>
+      </c>
+      <c r="B56" t="s">
+        <v>147</v>
+      </c>
+      <c r="C56">
+        <v>0.3</v>
+      </c>
+      <c r="D56" t="s">
+        <v>51</v>
+      </c>
+      <c r="E56" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" t="s">
+        <v>149</v>
+      </c>
+      <c r="B57" t="s">
+        <v>150</v>
+      </c>
+      <c r="C57">
+        <v>0.35</v>
+      </c>
+      <c r="D57" t="s">
+        <v>151</v>
+      </c>
+      <c r="E57" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" t="s">
+        <v>153</v>
+      </c>
+      <c r="B58" t="s">
+        <v>154</v>
+      </c>
+      <c r="C58">
+        <v>0.25</v>
+      </c>
+      <c r="D58" t="s">
+        <v>155</v>
+      </c>
+      <c r="E58" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" t="s">
+        <v>157</v>
+      </c>
+      <c r="B59" t="s">
+        <v>158</v>
+      </c>
+      <c r="C59">
+        <v>1.2</v>
+      </c>
+      <c r="D59" t="s">
+        <v>151</v>
+      </c>
+      <c r="E59" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" t="s">
+        <v>160</v>
+      </c>
+      <c r="B60" t="s">
+        <v>161</v>
+      </c>
+      <c r="C60">
+        <v>1.5</v>
+      </c>
+      <c r="D60" t="s">
+        <v>82</v>
+      </c>
+      <c r="E60" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" t="s">
+        <v>163</v>
+      </c>
+      <c r="B61" t="s">
+        <v>164</v>
+      </c>
+      <c r="C61">
+        <v>0.35</v>
+      </c>
+      <c r="D61" t="s">
+        <v>51</v>
+      </c>
+      <c r="E61" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" t="s">
+        <v>166</v>
+      </c>
+      <c r="B62" t="s">
+        <v>167</v>
+      </c>
+      <c r="C62">
+        <v>1.2</v>
+      </c>
+      <c r="D62" t="s">
+        <v>82</v>
+      </c>
+      <c r="E62" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" t="s">
+        <v>169</v>
+      </c>
+      <c r="B63" t="s">
+        <v>170</v>
+      </c>
+      <c r="C63">
+        <v>0.18</v>
+      </c>
+      <c r="D63" t="s">
+        <v>51</v>
+      </c>
+      <c r="E63" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" t="s">
+        <v>172</v>
+      </c>
+      <c r="B64" t="s">
+        <v>173</v>
+      </c>
+      <c r="C64">
+        <v>40</v>
+      </c>
+      <c r="D64" t="s">
+        <v>133</v>
+      </c>
+      <c r="E64" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" t="s">
+        <v>175</v>
+      </c>
+      <c r="B65" t="s">
+        <v>176</v>
+      </c>
+      <c r="C65">
+        <v>0.35</v>
+      </c>
+      <c r="D65" t="s">
+        <v>51</v>
+      </c>
+      <c r="E65" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -12213,7 +12525,7 @@
   <sheetData>
     <row r="1" ht="17.4" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>142</v>
+        <v>178</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -12243,40 +12555,40 @@
     </row>
     <row r="3" ht="42.6" spans="1:12">
       <c r="A3" s="4" t="s">
-        <v>143</v>
+        <v>179</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>144</v>
+        <v>180</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>145</v>
+        <v>181</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>146</v>
+        <v>182</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>147</v>
+        <v>183</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>148</v>
+        <v>184</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>149</v>
+        <v>185</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>150</v>
+        <v>186</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>152</v>
+        <v>188</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>27</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>153</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -16276,7 +16588,7 @@
   <sheetData>
     <row r="1" ht="17.4" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -16298,7 +16610,7 @@
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="21" t="s">
-        <v>155</v>
+        <v>191</v>
       </c>
       <c r="B2" s="15"/>
       <c r="C2" s="15"/>
@@ -16340,28 +16652,28 @@
     </row>
     <row r="4" ht="28.8" spans="1:18">
       <c r="A4" s="3" t="s">
-        <v>156</v>
+        <v>192</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>157</v>
+        <v>193</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>158</v>
+        <v>194</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>159</v>
+        <v>195</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>160</v>
+        <v>196</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>161</v>
+        <v>197</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>162</v>
+        <v>198</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>163</v>
+        <v>199</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>9</v>
@@ -17531,7 +17843,7 @@
       </c>
       <c r="N28" s="15"/>
       <c r="O28" s="12" t="s">
-        <v>164</v>
+        <v>200</v>
       </c>
       <c r="P28" s="15"/>
       <c r="Q28" s="15"/>
@@ -17584,13 +17896,13 @@
         <v>53</v>
       </c>
       <c r="P29" s="23" t="s">
-        <v>165</v>
+        <v>201</v>
       </c>
       <c r="Q29" s="23" t="s">
-        <v>166</v>
+        <v>202</v>
       </c>
       <c r="R29" s="23" t="s">
-        <v>167</v>
+        <v>203</v>
       </c>
     </row>
     <row r="30" spans="1:18">
@@ -18021,7 +18333,7 @@
       </c>
       <c r="N37" s="15"/>
       <c r="O37" s="11" t="s">
-        <v>168</v>
+        <v>204</v>
       </c>
       <c r="P37" s="15"/>
       <c r="Q37" s="15"/>
@@ -30864,7 +31176,7 @@
   <sheetData>
     <row r="1" ht="17.4" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>169</v>
+        <v>205</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -30878,7 +31190,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>170</v>
+        <v>206</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>31</v>
@@ -30887,145 +31199,145 @@
         <v>32</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>171</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="7" t="s">
-        <v>172</v>
+        <v>208</v>
       </c>
       <c r="B4" s="6">
         <v>10000</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>173</v>
+        <v>209</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>174</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="5" t="s">
-        <v>175</v>
+        <v>211</v>
       </c>
       <c r="B5" s="6">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>176</v>
+        <v>212</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>177</v>
+        <v>213</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="5" t="s">
-        <v>178</v>
+        <v>214</v>
       </c>
       <c r="B6" s="6">
         <v>10</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>179</v>
+        <v>215</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>180</v>
+        <v>216</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="5" t="s">
-        <v>181</v>
+        <v>217</v>
       </c>
       <c r="B7" s="6">
         <v>4</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>176</v>
+        <v>212</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>182</v>
+        <v>218</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="5" t="s">
-        <v>183</v>
+        <v>219</v>
       </c>
       <c r="B8" s="6">
         <v>6</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>179</v>
+        <v>215</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>184</v>
+        <v>220</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="5" t="s">
-        <v>185</v>
+        <v>221</v>
       </c>
       <c r="B9" s="16">
         <v>0.01</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>186</v>
+        <v>222</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>184</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="7" t="s">
-        <v>187</v>
+        <v>223</v>
       </c>
       <c r="B10" s="16">
         <v>0.01</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>188</v>
+        <v>224</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="5" t="s">
-        <v>190</v>
+        <v>226</v>
       </c>
       <c r="B11" s="6">
         <v>3</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>179</v>
+        <v>215</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>191</v>
+        <v>227</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="5" t="s">
-        <v>192</v>
+        <v>228</v>
       </c>
       <c r="B12" s="16">
         <v>0.15</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="7" t="s">
-        <v>193</v>
+        <v>229</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="5" t="s">
-        <v>194</v>
+        <v>230</v>
       </c>
       <c r="B13" s="6">
         <v>1380</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>195</v>
+        <v>231</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -31036,21 +31348,21 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="3" t="s">
-        <v>197</v>
+        <v>233</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>198</v>
+        <v>234</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>199</v>
+        <v>235</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>200</v>
+        <v>236</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="5" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="B16" s="17">
         <f>B4*B5*B6/1000</f>
@@ -31067,7 +31379,7 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="5" t="s">
-        <v>202</v>
+        <v>238</v>
       </c>
       <c r="B17" s="17">
         <f>B4*(1-B9)*B7*B8/1000</f>
@@ -31084,7 +31396,7 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="7" t="s">
-        <v>203</v>
+        <v>239</v>
       </c>
       <c r="B18" s="17">
         <f>B4*B10*B11*(1-B12)</f>
@@ -31101,7 +31413,7 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="12" t="s">
-        <v>204</v>
+        <v>240</v>
       </c>
       <c r="B19" s="18">
         <f>SUM(B16:B18)</f>
@@ -31118,7 +31430,7 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="5" t="s">
-        <v>205</v>
+        <v>241</v>
       </c>
       <c r="B20" s="19">
         <f>IF(B19&gt;0,(B16+B17)/B19,0)</f>
@@ -31129,7 +31441,7 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="7" t="s">
-        <v>206</v>
+        <v>242</v>
       </c>
       <c r="B21" s="20">
         <f>IF(B4&gt;0,B19/B4,0)</f>
@@ -31146,7 +31458,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>207</v>
+        <v>243</v>
       </c>
       <c r="B23" s="15"/>
       <c r="C23" s="15"/>
@@ -31174,29 +31486,29 @@
   <sheetData>
     <row r="1" ht="17.4" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>208</v>
+        <v>244</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="3" t="s">
-        <v>209</v>
+        <v>245</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>210</v>
+        <v>246</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>211</v>
+        <v>247</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>212</v>
+        <v>248</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>213</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="5" t="s">
-        <v>214</v>
+        <v>250</v>
       </c>
       <c r="B4" s="6">
         <v>7</v>
@@ -31209,12 +31521,12 @@
         <v>210</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>215</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="5" t="s">
-        <v>216</v>
+        <v>252</v>
       </c>
       <c r="B5" s="6">
         <v>7</v>
@@ -31230,7 +31542,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="7" t="s">
-        <v>217</v>
+        <v>253</v>
       </c>
       <c r="B6" s="6">
         <v>1</v>
@@ -31243,12 +31555,12 @@
         <v>100</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>218</v>
+        <v>254</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="5" t="s">
-        <v>219</v>
+        <v>255</v>
       </c>
       <c r="B7" s="6">
         <v>3</v>
@@ -31261,12 +31573,12 @@
         <v>60</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>220</v>
+        <v>256</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="5" t="s">
-        <v>221</v>
+        <v>257</v>
       </c>
       <c r="B8" s="6">
         <v>5</v>
@@ -31279,12 +31591,12 @@
         <v>25</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>222</v>
+        <v>258</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="12" t="s">
-        <v>223</v>
+        <v>259</v>
       </c>
       <c r="D9" s="12">
         <f>SUM(D4:D8)</f>
@@ -31293,22 +31605,22 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="3" t="s">
-        <v>224</v>
+        <v>260</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>225</v>
+        <v>261</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3" t="s">
-        <v>226</v>
+        <v>262</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>213</v>
+        <v>249</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="5" t="s">
-        <v>227</v>
+        <v>263</v>
       </c>
       <c r="B12" s="6">
         <v>100</v>
@@ -31318,12 +31630,12 @@
         <v>5.4</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>228</v>
+        <v>264</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="5" t="s">
-        <v>229</v>
+        <v>265</v>
       </c>
       <c r="B13" s="6">
         <v>300</v>
@@ -31336,7 +31648,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="5" t="s">
-        <v>230</v>
+        <v>266</v>
       </c>
       <c r="B14" s="6">
         <v>20</v>
@@ -31349,7 +31661,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="5" t="s">
-        <v>231</v>
+        <v>267</v>
       </c>
       <c r="B15" s="6">
         <v>150</v>
@@ -31362,24 +31674,24 @@
     </row>
     <row r="17" ht="28.2" spans="1:5">
       <c r="A17" s="3" t="s">
-        <v>232</v>
+        <v>268</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>233</v>
+        <v>269</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>234</v>
+        <v>270</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>235</v>
+        <v>271</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>236</v>
+        <v>272</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>237</v>
+        <v>273</v>
       </c>
       <c r="B18" s="13">
         <v>1200</v>
@@ -31398,7 +31710,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>238</v>
+        <v>274</v>
       </c>
       <c r="B19" s="13">
         <v>5900</v>
@@ -31417,7 +31729,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>239</v>
+        <v>275</v>
       </c>
       <c r="B20" s="13">
         <v>29000</v>
@@ -31436,7 +31748,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>240</v>
+        <v>276</v>
       </c>
       <c r="B21" s="13">
         <v>5900</v>
@@ -31455,7 +31767,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>241</v>
+        <v>277</v>
       </c>
       <c r="B22" s="13">
         <v>2500</v>
@@ -31474,7 +31786,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>242</v>
+        <v>278</v>
       </c>
       <c r="B23" s="13">
         <v>4400</v>
@@ -31493,7 +31805,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2" t="s">
-        <v>243</v>
+        <v>279</v>
       </c>
     </row>
   </sheetData>
@@ -31519,17 +31831,17 @@
   <sheetData>
     <row r="1" ht="17.4" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>244</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>245</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4" ht="28.2" spans="1:8">
       <c r="A4" s="3" t="s">
-        <v>246</v>
+        <v>282</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>31</v>
@@ -31540,88 +31852,88 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="5" t="s">
-        <v>247</v>
+        <v>283</v>
       </c>
       <c r="B5" s="6">
         <v>0.2</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>248</v>
+        <v>284</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="5" t="s">
-        <v>249</v>
+        <v>285</v>
       </c>
       <c r="B6" s="6">
         <v>0.15</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>250</v>
+        <v>286</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="5" t="s">
-        <v>251</v>
+        <v>287</v>
       </c>
       <c r="B7" s="6">
         <v>0.1</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>252</v>
+        <v>288</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="5" t="s">
-        <v>253</v>
+        <v>289</v>
       </c>
       <c r="B8" s="6">
         <v>8</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>254</v>
+        <v>290</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="5" t="s">
-        <v>255</v>
+        <v>291</v>
       </c>
       <c r="B9" s="6">
         <v>2</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>256</v>
+        <v>292</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="1:8">
       <c r="A11" s="3" t="s">
-        <v>257</v>
+        <v>293</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>258</v>
+        <v>294</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>259</v>
+        <v>295</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>260</v>
+        <v>296</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>261</v>
+        <v>297</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>262</v>
+        <v>298</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>263</v>
+        <v>299</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>264</v>
+        <v>300</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="5" t="s">
-        <v>265</v>
+        <v>301</v>
       </c>
       <c r="B12" s="8">
         <v>346</v>
@@ -31651,7 +31963,7 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="5" t="s">
-        <v>266</v>
+        <v>302</v>
       </c>
       <c r="B13" s="8">
         <v>1919</v>
@@ -31681,7 +31993,7 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="5" t="s">
-        <v>267</v>
+        <v>303</v>
       </c>
       <c r="B14" s="8">
         <v>7903</v>
@@ -31711,7 +32023,7 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="5" t="s">
-        <v>268</v>
+        <v>304</v>
       </c>
       <c r="B15" s="8">
         <v>24394</v>
@@ -31741,7 +32053,7 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="5" t="s">
-        <v>269</v>
+        <v>305</v>
       </c>
       <c r="B16" s="8">
         <v>84051</v>
@@ -31771,12 +32083,12 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="2" t="s">
-        <v>270</v>
+        <v>306</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="11" t="s">
-        <v>271</v>
+        <v>307</v>
       </c>
     </row>
   </sheetData>
@@ -31794,38 +32106,38 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>272</v>
+        <v>308</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>273</v>
+        <v>309</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>274</v>
+        <v>310</v>
       </c>
       <c r="B4" t="s">
-        <v>275</v>
+        <v>311</v>
       </c>
       <c r="C4" t="s">
-        <v>276</v>
+        <v>312</v>
       </c>
       <c r="D4" t="s">
-        <v>277</v>
+        <v>313</v>
       </c>
       <c r="E4" t="s">
-        <v>278</v>
+        <v>314</v>
       </c>
       <c r="F4" t="s">
-        <v>279</v>
+        <v>315</v>
       </c>
       <c r="G4" t="s">
-        <v>280</v>
+        <v>316</v>
       </c>
       <c r="H4" t="s">
-        <v>281</v>
+        <v>317</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -31931,7 +32243,7 @@
         <v>500</v>
       </c>
       <c r="D9" t="s">
-        <v>277</v>
+        <v>313</v>
       </c>
       <c r="E9">
         <v>13</v>
@@ -32049,7 +32361,7 @@
         <v>2000</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>313</v>
       </c>
       <c r="E14">
         <v>20</v>
@@ -32167,7 +32479,7 @@
         <v>6000</v>
       </c>
       <c r="D19" t="s">
-        <v>277</v>
+        <v>313</v>
       </c>
       <c r="E19">
         <v>29</v>
@@ -32285,7 +32597,7 @@
         <v>15000</v>
       </c>
       <c r="D24" t="s">
-        <v>277</v>
+        <v>313</v>
       </c>
       <c r="E24">
         <v>45</v>
@@ -32403,7 +32715,7 @@
         <v>40000</v>
       </c>
       <c r="D29" t="s">
-        <v>277</v>
+        <v>313</v>
       </c>
       <c r="E29">
         <v>113</v>
@@ -32420,30 +32732,30 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" t="s">
-        <v>282</v>
+        <v>318</v>
       </c>
       <c r="B32" t="s">
-        <v>283</v>
+        <v>319</v>
       </c>
       <c r="C32">
         <v>1.3</v>
       </c>
       <c r="D32" t="s">
-        <v>284</v>
+        <v>320</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>285</v>
+        <v>321</v>
       </c>
       <c r="B34" t="s">
-        <v>286</v>
+        <v>322</v>
       </c>
       <c r="C34" t="s">
-        <v>287</v>
+        <v>323</v>
       </c>
       <c r="D34" t="s">
-        <v>288</v>
+        <v>324</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -32451,7 +32763,7 @@
         <v>2</v>
       </c>
       <c r="B35" t="s">
-        <v>289</v>
+        <v>325</v>
       </c>
       <c r="C35">
         <v>8</v>
@@ -32462,7 +32774,7 @@
         <v>3</v>
       </c>
       <c r="B36" t="s">
-        <v>289</v>
+        <v>325</v>
       </c>
       <c r="C36">
         <v>20</v>
@@ -32473,7 +32785,7 @@
         <v>4</v>
       </c>
       <c r="B37" t="s">
-        <v>289</v>
+        <v>325</v>
       </c>
       <c r="C37">
         <v>32</v>
@@ -32484,7 +32796,7 @@
         <v>5</v>
       </c>
       <c r="B38" t="s">
-        <v>289</v>
+        <v>325</v>
       </c>
       <c r="C38">
         <v>45</v>
@@ -32495,7 +32807,7 @@
         <v>6</v>
       </c>
       <c r="B39" t="s">
-        <v>289</v>
+        <v>325</v>
       </c>
       <c r="C39">
         <v>60</v>

--- a/모찌런처_밸런스시트.xlsx
+++ b/모찌런처_밸런스시트.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="393">
   <si>
     <t>모찌 런처 — 밸런스 설정값</t>
   </si>
@@ -4245,6 +4245,168 @@
     <t>스테이지당 판수(광고100%)</t>
   </si>
   <si>
+    <t>★★★ 미션 (JSON, GDD §4 미션 타입)</t>
+  </si>
+  <si>
+    <t>★★★ 미션 설명</t>
+  </si>
+  <si>
+    <t>[{"type":"grade_min","grade":"perfect"}]</t>
+  </si>
+  <si>
+    <t>PERFECT 발사로 클리어</t>
+  </si>
+  <si>
+    <t>[{"type":"seeds_min","n":5}]</t>
+  </si>
+  <si>
+    <t>씨앗 5개 모으기</t>
+  </si>
+  <si>
+    <t>[{"type":"hit","obj":"tramp","n":2}]</t>
+  </si>
+  <si>
+    <t>트램폴린 2회</t>
+  </si>
+  <si>
+    <t>[{"type":"hit","obj":"clothesline","n":2}]</t>
+  </si>
+  <si>
+    <t>빨랫줄 2회 튕기기</t>
+  </si>
+  <si>
+    <t>[{"type":"no_boost"}]</t>
+  </si>
+  <si>
+    <t>부스터를 쓰지 않고 클리어</t>
+  </si>
+  <si>
+    <t>[{"type":"hit","obj":"balloon","n":2}]</t>
+  </si>
+  <si>
+    <t>풍선 2개</t>
+  </si>
+  <si>
+    <t>[{"type":"glide_sec","sec":3}]</t>
+  </si>
+  <si>
+    <t>볼 부풀리기 활공 누적 3초</t>
+  </si>
+  <si>
+    <t>[{"type":"hit","obj":"fountain","n":2}]</t>
+  </si>
+  <si>
+    <t>분수 2회</t>
+  </si>
+  <si>
+    <t>[{"type":"dive_perfect","n":1}]</t>
+  </si>
+  <si>
+    <t>급강하 퍼펙트 1회</t>
+  </si>
+  <si>
+    <t>[{"type":"boss_margin_sec","sec":3}]</t>
+  </si>
+  <si>
+    <t>대장보다 3초 이상 먼저 골인</t>
+  </si>
+  <si>
+    <t>[{"type":"hit","obj":"updraft","n":2}]</t>
+  </si>
+  <si>
+    <t>실외기 상승기류 2회</t>
+  </si>
+  <si>
+    <t>[{"type":"no_hit","obj":"crow"}]</t>
+  </si>
+  <si>
+    <t>까마귀에게 한 번도 안 부딪히기</t>
+  </si>
+  <si>
+    <t>[{"type":"hit","obj":"billboard","n":1},{"type":"seeds_min","n":40}]</t>
+  </si>
+  <si>
+    <t>광고판 씨앗 폭발 1회 + 씨앗 40개</t>
+  </si>
+  <si>
+    <t>[{"type":"combo_min","n":6}]</t>
+  </si>
+  <si>
+    <t>콤보 6</t>
+  </si>
+  <si>
+    <t>[{"type":"boss_meter_max","ratio":0.5}]</t>
+  </si>
+  <si>
+    <t>훔친 씨앗 게이지 50% 미만으로 클리어</t>
+  </si>
+  <si>
+    <t>[{"type":"hit","obj":"cloud_tramp","n":3}]</t>
+  </si>
+  <si>
+    <t>구름 트램폴린 3회</t>
+  </si>
+  <si>
+    <t>[{"type":"ride_full","obj":"rainbow","n":1}]</t>
+  </si>
+  <si>
+    <t>무지개 레일 끝까지 타기</t>
+  </si>
+  <si>
+    <t>[{"type":"no_hit","obj":"thundercloud"}]</t>
+  </si>
+  <si>
+    <t>번개구름 0회</t>
+  </si>
+  <si>
+    <t>[{"type":"overcharge_perfect","power":1.05}]</t>
+  </si>
+  <si>
+    <t>힘 105% 이상으로 PERFECT 발사</t>
+  </si>
+  <si>
+    <t>[{"type":"no_hit","obj":"lightning"}]</t>
+  </si>
+  <si>
+    <t>번개 피격 0회로 클리어</t>
+  </si>
+  <si>
+    <t>[{"type":"hit","obj":"satellite","n":3}]</t>
+  </si>
+  <si>
+    <t>인공위성 바운스 3회</t>
+  </si>
+  <si>
+    <t>[{"type":"fuel_left_min","ratio":0.5}]</t>
+  </si>
+  <si>
+    <t>부스터 연료 50% 이상 남기고 클리어</t>
+  </si>
+  <si>
+    <t>[{"type":"no_hit","obj":"meteor"}]</t>
+  </si>
+  <si>
+    <t>운석 0회</t>
+  </si>
+  <si>
+    <t>[{"type":"combo_min","n":10}]</t>
+  </si>
+  <si>
+    <t>콤보 10</t>
+  </si>
+  <si>
+    <t>[{"type":"boss_perfect_all","n":3}]</t>
+  </si>
+  <si>
+    <t>블랙홀 3개 모두 퍼펙트 탈출</t>
+  </si>
+  <si>
+    <t>[{"type":"land_in_zone","radius_m":50}]</t>
+  </si>
+  <si>
+    <t>착륙 패드(±50m) 안에 멈추기 — ★ 달 도달 / ★★ 씨앗 100개 / ★★★ 착륙 패드</t>
+  </si>
+  <si>
     <t>★★ 목표 배율</t>
   </si>
   <si>
@@ -4267,6 +4429,45 @@
   </si>
   <si>
     <t>world_unlock_stars</t>
+  </si>
+  <si>
+    <t>보스 (GDD §4 보스 스테이지 상세)</t>
+  </si>
+  <si>
+    <t>2-5 대장 골인 시간</t>
+  </si>
+  <si>
+    <t>boss_2_5_rival_time_sec</t>
+  </si>
+  <si>
+    <t>대장이 0→2,000m 에 걸리는 시간(초). 플레이테스트로 확정</t>
+  </si>
+  <si>
+    <t>2-5 비둘기 배치 배율</t>
+  </si>
+  <si>
+    <t>boss_2_5_pigeon_mult</t>
+  </si>
+  <si>
+    <t>보통 공원 대비 비둘기 수</t>
+  </si>
+  <si>
+    <t>보스 연속 실패 완화 단계</t>
+  </si>
+  <si>
+    <t>boss_fail_ease_step</t>
+  </si>
+  <si>
+    <t>3판 연속 실패마다 난이도 5% 완화</t>
+  </si>
+  <si>
+    <t>보스 완화 최대</t>
+  </si>
+  <si>
+    <t>boss_fail_ease_max</t>
+  </si>
+  <si>
+    <t>최대 15%. 클리어하면 초기화</t>
   </si>
 </sst>
 </file>
@@ -32101,20 +32302,20 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H39"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <dimension ref="A1:J45"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>310</v>
       </c>
@@ -32139,8 +32340,14 @@
       <c r="H4" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4" t="s">
+        <v>318</v>
+      </c>
+      <c r="J4" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5">
         <v>1</v>
       </c>
@@ -32162,8 +32369,14 @@
       <c r="H5">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5" t="s">
+        <v>320</v>
+      </c>
+      <c r="J5" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6">
         <v>1</v>
       </c>
@@ -32185,8 +32398,14 @@
       <c r="H6">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6" t="s">
+        <v>322</v>
+      </c>
+      <c r="J6" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7">
         <v>1</v>
       </c>
@@ -32208,8 +32427,14 @@
       <c r="H7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="I7" t="s">
+        <v>324</v>
+      </c>
+      <c r="J7" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8">
         <v>1</v>
       </c>
@@ -32231,8 +32456,14 @@
       <c r="H8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="I8" t="s">
+        <v>326</v>
+      </c>
+      <c r="J8" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9">
         <v>1</v>
       </c>
@@ -32257,8 +32488,14 @@
       <c r="H9">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="I9" t="s">
+        <v>328</v>
+      </c>
+      <c r="J9" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10">
         <v>2</v>
       </c>
@@ -32280,8 +32517,14 @@
       <c r="H10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="I10" t="s">
+        <v>330</v>
+      </c>
+      <c r="J10" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11">
         <v>2</v>
       </c>
@@ -32303,8 +32546,14 @@
       <c r="H11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="I11" t="s">
+        <v>332</v>
+      </c>
+      <c r="J11" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12">
         <v>2</v>
       </c>
@@ -32326,8 +32575,14 @@
       <c r="H12">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="I12" t="s">
+        <v>334</v>
+      </c>
+      <c r="J12" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13">
         <v>2</v>
       </c>
@@ -32349,8 +32604,14 @@
       <c r="H13">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="I13" t="s">
+        <v>336</v>
+      </c>
+      <c r="J13" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14">
         <v>2</v>
       </c>
@@ -32375,8 +32636,14 @@
       <c r="H14">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:8">
+      <c r="I14" t="s">
+        <v>338</v>
+      </c>
+      <c r="J14" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15">
         <v>3</v>
       </c>
@@ -32398,8 +32665,14 @@
       <c r="H15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:8">
+      <c r="I15" t="s">
+        <v>340</v>
+      </c>
+      <c r="J15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16">
         <v>3</v>
       </c>
@@ -32421,8 +32694,14 @@
       <c r="H16">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:8">
+      <c r="I16" t="s">
+        <v>342</v>
+      </c>
+      <c r="J16" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17">
         <v>3</v>
       </c>
@@ -32444,8 +32723,14 @@
       <c r="H17">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:8">
+      <c r="I17" t="s">
+        <v>344</v>
+      </c>
+      <c r="J17" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18">
         <v>3</v>
       </c>
@@ -32467,8 +32752,14 @@
       <c r="H18">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:8">
+      <c r="I18" t="s">
+        <v>346</v>
+      </c>
+      <c r="J18" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19">
         <v>3</v>
       </c>
@@ -32493,8 +32784,14 @@
       <c r="H19">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:8">
+      <c r="I19" t="s">
+        <v>348</v>
+      </c>
+      <c r="J19" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20">
         <v>4</v>
       </c>
@@ -32516,8 +32813,14 @@
       <c r="H20">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:8">
+      <c r="I20" t="s">
+        <v>350</v>
+      </c>
+      <c r="J20" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21">
         <v>4</v>
       </c>
@@ -32539,8 +32842,14 @@
       <c r="H21">
         <v>2</v>
       </c>
-    </row>
-    <row r="22" spans="1:8">
+      <c r="I21" t="s">
+        <v>352</v>
+      </c>
+      <c r="J21" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22">
         <v>4</v>
       </c>
@@ -32562,8 +32871,14 @@
       <c r="H22">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:8">
+      <c r="I22" t="s">
+        <v>354</v>
+      </c>
+      <c r="J22" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23">
         <v>4</v>
       </c>
@@ -32585,8 +32900,14 @@
       <c r="H23">
         <v>2</v>
       </c>
-    </row>
-    <row r="24" spans="1:8">
+      <c r="I23" t="s">
+        <v>356</v>
+      </c>
+      <c r="J23" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24">
         <v>4</v>
       </c>
@@ -32611,8 +32932,14 @@
       <c r="H24">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:8">
+      <c r="I24" t="s">
+        <v>358</v>
+      </c>
+      <c r="J24" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25">
         <v>5</v>
       </c>
@@ -32634,8 +32961,14 @@
       <c r="H25">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:8">
+      <c r="I25" t="s">
+        <v>360</v>
+      </c>
+      <c r="J25" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26">
         <v>5</v>
       </c>
@@ -32657,8 +32990,14 @@
       <c r="H26">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="1:8">
+      <c r="I26" t="s">
+        <v>362</v>
+      </c>
+      <c r="J26" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27">
         <v>5</v>
       </c>
@@ -32680,8 +33019,14 @@
       <c r="H27">
         <v>7</v>
       </c>
-    </row>
-    <row r="28" spans="1:8">
+      <c r="I27" t="s">
+        <v>364</v>
+      </c>
+      <c r="J27" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28">
         <v>5</v>
       </c>
@@ -32703,8 +33048,14 @@
       <c r="H28">
         <v>8</v>
       </c>
-    </row>
-    <row r="29" spans="1:8">
+      <c r="I28" t="s">
+        <v>366</v>
+      </c>
+      <c r="J28" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29">
         <v>5</v>
       </c>
@@ -32729,33 +33080,56 @@
       <c r="H29">
         <v>12</v>
       </c>
-    </row>
-    <row r="32" spans="1:8">
+      <c r="I29" t="s">
+        <v>368</v>
+      </c>
+      <c r="J29" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30">
+        <v>6</v>
+      </c>
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="D30" t="s">
+        <v>305</v>
+      </c>
+      <c r="I30" t="s">
+        <v>370</v>
+      </c>
+      <c r="J30" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="B32" t="s">
-        <v>319</v>
+        <v>373</v>
       </c>
       <c r="C32">
         <v>1.3</v>
       </c>
       <c r="D32" t="s">
-        <v>320</v>
+        <v>374</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>321</v>
+        <v>375</v>
       </c>
       <c r="B34" t="s">
-        <v>322</v>
+        <v>376</v>
       </c>
       <c r="C34" t="s">
-        <v>323</v>
+        <v>377</v>
       </c>
       <c r="D34" t="s">
-        <v>324</v>
+        <v>378</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -32763,7 +33137,7 @@
         <v>2</v>
       </c>
       <c r="B35" t="s">
-        <v>325</v>
+        <v>379</v>
       </c>
       <c r="C35">
         <v>8</v>
@@ -32774,7 +33148,7 @@
         <v>3</v>
       </c>
       <c r="B36" t="s">
-        <v>325</v>
+        <v>379</v>
       </c>
       <c r="C36">
         <v>20</v>
@@ -32785,7 +33159,7 @@
         <v>4</v>
       </c>
       <c r="B37" t="s">
-        <v>325</v>
+        <v>379</v>
       </c>
       <c r="C37">
         <v>32</v>
@@ -32796,7 +33170,7 @@
         <v>5</v>
       </c>
       <c r="B38" t="s">
-        <v>325</v>
+        <v>379</v>
       </c>
       <c r="C38">
         <v>45</v>
@@ -32807,10 +33181,80 @@
         <v>6</v>
       </c>
       <c r="B39" t="s">
-        <v>325</v>
+        <v>379</v>
       </c>
       <c r="C39">
         <v>60</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" t="s">
+        <v>380</v>
+      </c>
+      <c r="B41" t="s">
+        <v>376</v>
+      </c>
+      <c r="C41" t="s">
+        <v>31</v>
+      </c>
+      <c r="D41" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" t="s">
+        <v>381</v>
+      </c>
+      <c r="B42" t="s">
+        <v>382</v>
+      </c>
+      <c r="C42">
+        <v>16</v>
+      </c>
+      <c r="D42" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" t="s">
+        <v>384</v>
+      </c>
+      <c r="B43" t="s">
+        <v>385</v>
+      </c>
+      <c r="C43">
+        <v>1.5</v>
+      </c>
+      <c r="D43" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" t="s">
+        <v>387</v>
+      </c>
+      <c r="B44" t="s">
+        <v>388</v>
+      </c>
+      <c r="C44">
+        <v>0.05</v>
+      </c>
+      <c r="D44" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" t="s">
+        <v>390</v>
+      </c>
+      <c r="B45" t="s">
+        <v>391</v>
+      </c>
+      <c r="C45">
+        <v>0.15</v>
+      </c>
+      <c r="D45" t="s">
+        <v>392</v>
       </c>
     </row>
   </sheetData>

--- a/모찌런처_밸런스시트.xlsx
+++ b/모찌런처_밸런스시트.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="6" activeTab="6"/>
+    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="7" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="설정" sheetId="1" r:id="rId1"/>
@@ -14,6 +14,7 @@
     <sheet name="별사탕 경제" sheetId="5" r:id="rId5"/>
     <sheet name="햄스터 마을" sheetId="6" r:id="rId6"/>
     <sheet name="스테이지" sheetId="7" r:id="rId7"/>
+    <sheet name="오브젝트" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="475">
   <si>
     <t>모찌 런처 — 밸런스 설정값</t>
   </si>
@@ -1163,6 +1164,18 @@
     <t>계산식: 샘플v / (v0×시간배율). 가상 화면 높이 540 기준 Lv0 줌. 속도·고도에 따라 줌아웃</t>
   </si>
   <si>
+    <t>샘플 모찌 반지름</t>
+  </si>
+  <si>
+    <t>mochi_radius_px</t>
+  </si>
+  <si>
+    <t>가상 px</t>
+  </si>
+  <si>
+    <t>2.5D 샘플 RAD. 충돌 반지름(m) = 이 값 / cam_base_px_per_m</t>
+  </si>
+  <si>
     <t>정확도 게이지·당기기 (GDD §2)</t>
   </si>
   <si>
@@ -1296,9 +1309,6 @@
   </si>
   <si>
     <t>pull_max_px</t>
-  </si>
-  <si>
-    <t>가상 px</t>
   </si>
   <si>
     <t>샘플 MAXPULL. 이 거리에서 힘 110%</t>
@@ -4468,6 +4478,243 @@
   </si>
   <si>
     <t>최대 15%. 클리어하면 초기화</t>
+  </si>
+  <si>
+    <t>오브젝트 — 효과·배치 (GDD §4 월드 테마·배치 규칙, 월드 1~3)</t>
+  </si>
+  <si>
+    <t>GDD 에 수치가 없어 2.5D 샘플(트램폴린·풍선)과 설계값으로 정함. 크기·높이·간격은 거리 배율 s(x) 로 커진다: s = max(1, 간격 / 기준 간격). 속도 단위 m/s (샘플 px/s ÷ 86.6 = 카메라 52.6px/m × 시간배율 1.648).</t>
+  </si>
+  <si>
+    <t>이름</t>
+  </si>
+  <si>
+    <t>분류</t>
+  </si>
+  <si>
+    <t>반지름(m)</t>
+  </si>
+  <si>
+    <t>값1</t>
+  </si>
+  <si>
+    <t>값2</t>
+  </si>
+  <si>
+    <t>값3</t>
+  </si>
+  <si>
+    <t>seed</t>
+  </si>
+  <si>
+    <t>씨앗</t>
+  </si>
+  <si>
+    <t>pickup</t>
+  </si>
+  <si>
+    <t>먹으면 씨앗 1개(콤보 배율 적용). 5개씩 호 모양 줄</t>
+  </si>
+  <si>
+    <t>tramp</t>
+  </si>
+  <si>
+    <t>트램폴린</t>
+  </si>
+  <si>
+    <t>bounce</t>
+  </si>
+  <si>
+    <t>땅 위. 위에서 닿으면 낙하 속도×값1(최소 값2 m/s)로 튕김, 수평×값3 (샘플)</t>
+  </si>
+  <si>
+    <t>clothesline</t>
+  </si>
+  <si>
+    <t>빨랫줄</t>
+  </si>
+  <si>
+    <t>공중 줄. 위에서 닿으면 튕김(×값1, 최소 값2), 앞으로 수평×값3</t>
+  </si>
+  <si>
+    <t>balloon</t>
+  </si>
+  <si>
+    <t>풍선</t>
+  </si>
+  <si>
+    <t>lift</t>
+  </si>
+  <si>
+    <t>상승: 위 속도 ≥ max(값1, 속력×값2), 수평 +값3 m/s (샘플)</t>
+  </si>
+  <si>
+    <t>fountain</t>
+  </si>
+  <si>
+    <t>분수</t>
+  </si>
+  <si>
+    <t>땅 위 수직 발사: 위 속도 ≥ max(값1, 속력×값2)</t>
+  </si>
+  <si>
+    <t>pigeon</t>
+  </si>
+  <si>
+    <t>비둘기</t>
+  </si>
+  <si>
+    <t>boost</t>
+  </si>
+  <si>
+    <t>올라타기: 수평×값1, 위 속도 ≥ 값2 (GDD 2-5 “올라타면 가속”)</t>
+  </si>
+  <si>
+    <t>updraft</t>
+  </si>
+  <si>
+    <t>실외기 상승기류</t>
+  </si>
+  <si>
+    <t>area</t>
+  </si>
+  <si>
+    <t>땅에서 높이 값2(×s) 까지 기둥, 안에 있으면 위로 값1 m/s² 가속</t>
+  </si>
+  <si>
+    <t>umbrella</t>
+  </si>
+  <si>
+    <t>빨간 우산</t>
+  </si>
+  <si>
+    <t>glide</t>
+  </si>
+  <si>
+    <t>값1초 동안 완전 활공(낙하 ≤ 수평×값2, 감속 없음)</t>
+  </si>
+  <si>
+    <t>billboard</t>
+  </si>
+  <si>
+    <t>광고판</t>
+  </si>
+  <si>
+    <t>seeds</t>
+  </si>
+  <si>
+    <t>충돌 시 씨앗 폭발 +값1개, 수평 감속 값2</t>
+  </si>
+  <si>
+    <t>branch</t>
+  </si>
+  <si>
+    <t>나뭇가지</t>
+  </si>
+  <si>
+    <t>obstacle</t>
+  </si>
+  <si>
+    <t>장애물: 수평 속도 −값1 비율 (비행은 계속)</t>
+  </si>
+  <si>
+    <t>wire</t>
+  </si>
+  <si>
+    <t>전선</t>
+  </si>
+  <si>
+    <t>장애물: 수평 −값1, 아래로 값2 m/s</t>
+  </si>
+  <si>
+    <t>crow</t>
+  </si>
+  <si>
+    <t>까마귀</t>
+  </si>
+  <si>
+    <t>장애물: 수평 −값1, 모은 씨앗 값2개 강탈</t>
+  </si>
+  <si>
+    <t>배치 (GDD §4 배치 규칙)</t>
+  </si>
+  <si>
+    <t>청크 길이</t>
+  </si>
+  <si>
+    <t>spawn_chunk_m</t>
+  </si>
+  <si>
+    <t>m. 청크마다 (런 시드, 청크 번호) 로 결정론 배치</t>
+  </si>
+  <si>
+    <t>최소 간격</t>
+  </si>
+  <si>
+    <t>spawn_min_spacing_m</t>
+  </si>
+  <si>
+    <t>m. 오브젝트 사이 간격 = max(최소, 거리×비율) ± 30%</t>
+  </si>
+  <si>
+    <t>간격 비율</t>
+  </si>
+  <si>
+    <t>spawn_spacing_ratio</t>
+  </si>
+  <si>
+    <t>거리 x 에서 간격 = x × 0.08 (멀리 갈수록 성기고 커짐)</t>
+  </si>
+  <si>
+    <t>기준 간격</t>
+  </si>
+  <si>
+    <t>spawn_scale_ref_m</t>
+  </si>
+  <si>
+    <t>m. 거리 배율 s = max(1, 간격 / 기준 간격) — 크기·높이에 곱함</t>
+  </si>
+  <si>
+    <t>최저 높이</t>
+  </si>
+  <si>
+    <t>spawn_min_h_m</t>
+  </si>
+  <si>
+    <t>높이 기본</t>
+  </si>
+  <si>
+    <t>spawn_h_base_m</t>
+  </si>
+  <si>
+    <t>m. 최고 높이 = 기본 + 거리 × 높이 비율</t>
+  </si>
+  <si>
+    <t>높이 비율</t>
+  </si>
+  <si>
+    <t>spawn_h_ratio</t>
+  </si>
+  <si>
+    <t>45° 궤적 최고점 ≈ 거리/4 → 궤적 안에 들어오게</t>
+  </si>
+  <si>
+    <t>씨앗 줄 개수</t>
+  </si>
+  <si>
+    <t>seed_row_count</t>
+  </si>
+  <si>
+    <t>샘플과 같음</t>
+  </si>
+  <si>
+    <t>월드별 배치 비중 (장애물 비율은 GDD: 0% → 30%, 공원 최대 10%)</t>
+  </si>
+  <si>
+    <t>obstacle_ratio</t>
+  </si>
+  <si>
+    <t>※ 장애물(분류 obstacle) 비중은 장애물끼리, 나머지는 나머지끼리 정규화. 월드 4~6 은 P11.</t>
   </si>
 </sst>
 </file>
@@ -12192,9 +12439,26 @@
         <v>87</v>
       </c>
     </row>
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
+        <v>88</v>
+      </c>
+      <c r="B33" t="s">
+        <v>89</v>
+      </c>
+      <c r="C33">
+        <v>38</v>
+      </c>
+      <c r="D33" t="s">
+        <v>90</v>
+      </c>
+      <c r="E33" t="s">
+        <v>91</v>
+      </c>
+    </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B34" t="s">
         <v>30</v>
@@ -12211,10 +12475,10 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B35" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C35">
         <v>1.1</v>
@@ -12223,49 +12487,49 @@
         <v>82</v>
       </c>
       <c r="E35" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B36" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C36">
         <v>0.45</v>
       </c>
       <c r="D36" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E36" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B37" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C37">
         <v>1.35</v>
       </c>
       <c r="D37" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E37" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B38" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C38">
         <v>9</v>
@@ -12274,66 +12538,66 @@
         <v>82</v>
       </c>
       <c r="E38" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B39" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C39">
         <v>0.1</v>
       </c>
       <c r="D39" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E39" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B40" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C40">
         <v>0.3</v>
       </c>
       <c r="D40" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E40" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B41" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C41">
         <v>0.6</v>
       </c>
       <c r="D41" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E41" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B42" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C42">
         <v>1.15</v>
@@ -12344,10 +12608,10 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B43" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C43">
         <v>1.03</v>
@@ -12356,15 +12620,15 @@
         <v>82</v>
       </c>
       <c r="E43" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B44" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C44">
         <v>1.13</v>
@@ -12373,15 +12637,15 @@
         <v>82</v>
       </c>
       <c r="E44" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B45" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C45">
         <v>0.95</v>
@@ -12392,10 +12656,10 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B46" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C46">
         <v>1.03</v>
@@ -12406,10 +12670,10 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B47" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C47">
         <v>0.8</v>
@@ -12420,10 +12684,10 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B48" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C48">
         <v>0.95</v>
@@ -12434,10 +12698,10 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B49" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C49">
         <v>0.5</v>
@@ -12446,32 +12710,32 @@
         <v>19</v>
       </c>
       <c r="E49" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B50" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C50">
         <v>150</v>
       </c>
       <c r="D50" t="s">
-        <v>133</v>
+        <v>90</v>
       </c>
       <c r="E50" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B51" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C51">
         <v>0.08</v>
@@ -12480,29 +12744,29 @@
         <v>82</v>
       </c>
       <c r="E51" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B52" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C52">
         <v>85</v>
       </c>
       <c r="D52" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E52" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B54" t="s">
         <v>30</v>
@@ -12519,10 +12783,10 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B55" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C55">
         <v>1.5</v>
@@ -12531,15 +12795,15 @@
         <v>51</v>
       </c>
       <c r="E55" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B56" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C56">
         <v>0.3</v>
@@ -12548,66 +12812,66 @@
         <v>51</v>
       </c>
       <c r="E56" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B57" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C57">
         <v>0.35</v>
       </c>
       <c r="D57" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E57" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B58" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C58">
         <v>0.25</v>
       </c>
       <c r="D58" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E58" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B59" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C59">
         <v>1.2</v>
       </c>
       <c r="D59" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E59" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B60" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C60">
         <v>1.5</v>
@@ -12616,15 +12880,15 @@
         <v>82</v>
       </c>
       <c r="E60" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B61" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C61">
         <v>0.35</v>
@@ -12633,15 +12897,15 @@
         <v>51</v>
       </c>
       <c r="E61" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B62" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C62">
         <v>1.2</v>
@@ -12650,15 +12914,15 @@
         <v>82</v>
       </c>
       <c r="E62" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B63" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C63">
         <v>0.18</v>
@@ -12667,32 +12931,32 @@
         <v>51</v>
       </c>
       <c r="E63" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B64" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C64">
         <v>40</v>
       </c>
       <c r="D64" t="s">
-        <v>133</v>
+        <v>90</v>
       </c>
       <c r="E64" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B65" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C65">
         <v>0.35</v>
@@ -12701,7 +12965,7 @@
         <v>51</v>
       </c>
       <c r="E65" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -12726,7 +12990,7 @@
   <sheetData>
     <row r="1" ht="17.4" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -12756,40 +13020,40 @@
     </row>
     <row r="3" ht="42.6" spans="1:12">
       <c r="A3" s="4" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>27</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -16789,7 +17053,7 @@
   <sheetData>
     <row r="1" ht="17.4" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -16811,7 +17075,7 @@
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="21" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B2" s="15"/>
       <c r="C2" s="15"/>
@@ -16853,28 +17117,28 @@
     </row>
     <row r="4" ht="28.8" spans="1:18">
       <c r="A4" s="3" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>9</v>
@@ -18044,7 +18308,7 @@
       </c>
       <c r="N28" s="15"/>
       <c r="O28" s="12" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="P28" s="15"/>
       <c r="Q28" s="15"/>
@@ -18097,13 +18361,13 @@
         <v>53</v>
       </c>
       <c r="P29" s="23" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q29" s="23" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="R29" s="23" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="30" spans="1:18">
@@ -18534,7 +18798,7 @@
       </c>
       <c r="N37" s="15"/>
       <c r="O37" s="11" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="P37" s="15"/>
       <c r="Q37" s="15"/>
@@ -31377,7 +31641,7 @@
   <sheetData>
     <row r="1" ht="17.4" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -31391,7 +31655,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>31</v>
@@ -31400,145 +31664,145 @@
         <v>32</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="7" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B4" s="6">
         <v>10000</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="5" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B5" s="6">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="5" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B6" s="6">
         <v>10</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="5" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B7" s="6">
         <v>4</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="5" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B8" s="6">
         <v>6</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="5" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B9" s="16">
         <v>0.01</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="7" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B10" s="16">
         <v>0.01</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="5" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B11" s="6">
         <v>3</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="5" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B12" s="16">
         <v>0.15</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="7" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="5" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B13" s="6">
         <v>1380</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -31549,21 +31813,21 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="3" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="5" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B16" s="17">
         <f>B4*B5*B6/1000</f>
@@ -31580,7 +31844,7 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="5" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B17" s="17">
         <f>B4*(1-B9)*B7*B8/1000</f>
@@ -31597,7 +31861,7 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="7" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B18" s="17">
         <f>B4*B10*B11*(1-B12)</f>
@@ -31614,7 +31878,7 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="12" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B19" s="18">
         <f>SUM(B16:B18)</f>
@@ -31631,7 +31895,7 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="5" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B20" s="19">
         <f>IF(B19&gt;0,(B16+B17)/B19,0)</f>
@@ -31642,7 +31906,7 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="7" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B21" s="20">
         <f>IF(B4&gt;0,B19/B4,0)</f>
@@ -31659,7 +31923,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B23" s="15"/>
       <c r="C23" s="15"/>
@@ -31687,29 +31951,29 @@
   <sheetData>
     <row r="1" ht="17.4" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="3" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="5" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B4" s="6">
         <v>7</v>
@@ -31722,12 +31986,12 @@
         <v>210</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="5" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B5" s="6">
         <v>7</v>
@@ -31743,7 +32007,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="7" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B6" s="6">
         <v>1</v>
@@ -31756,12 +32020,12 @@
         <v>100</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="5" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B7" s="6">
         <v>3</v>
@@ -31774,12 +32038,12 @@
         <v>60</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="5" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B8" s="6">
         <v>5</v>
@@ -31792,12 +32056,12 @@
         <v>25</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="12" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D9" s="12">
         <f>SUM(D4:D8)</f>
@@ -31806,22 +32070,22 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="3" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="5" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B12" s="6">
         <v>100</v>
@@ -31831,12 +32095,12 @@
         <v>5.4</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="5" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B13" s="6">
         <v>300</v>
@@ -31849,7 +32113,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="5" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B14" s="6">
         <v>20</v>
@@ -31862,7 +32126,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="5" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B15" s="6">
         <v>150</v>
@@ -31875,24 +32139,24 @@
     </row>
     <row r="17" ht="28.2" spans="1:5">
       <c r="A17" s="3" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B18" s="13">
         <v>1200</v>
@@ -31911,7 +32175,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B19" s="13">
         <v>5900</v>
@@ -31930,7 +32194,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B20" s="13">
         <v>29000</v>
@@ -31949,7 +32213,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B21" s="13">
         <v>5900</v>
@@ -31968,7 +32232,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B22" s="13">
         <v>2500</v>
@@ -31987,7 +32251,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B23" s="13">
         <v>4400</v>
@@ -32006,7 +32270,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
   </sheetData>
@@ -32032,17 +32296,17 @@
   <sheetData>
     <row r="1" ht="17.4" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="4" ht="28.2" spans="1:8">
       <c r="A4" s="3" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>31</v>
@@ -32053,88 +32317,88 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="5" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B5" s="6">
         <v>0.2</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="5" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B6" s="6">
         <v>0.15</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="5" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B7" s="6">
         <v>0.1</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="5" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B8" s="6">
         <v>8</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="5" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B9" s="6">
         <v>2</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="1:8">
       <c r="A11" s="3" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="5" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B12" s="8">
         <v>346</v>
@@ -32164,7 +32428,7 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="5" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B13" s="8">
         <v>1919</v>
@@ -32194,7 +32458,7 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="5" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B14" s="8">
         <v>7903</v>
@@ -32224,7 +32488,7 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="5" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B15" s="8">
         <v>24394</v>
@@ -32254,7 +32518,7 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="5" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B16" s="8">
         <v>84051</v>
@@ -32284,12 +32548,12 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="2" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="11" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
   </sheetData>
@@ -32307,44 +32571,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B4" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="C4" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="D4" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E4" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="F4" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="G4" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="H4" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="I4" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="J4" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -32370,10 +32634,10 @@
         <v>3</v>
       </c>
       <c r="I5" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="J5" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -32399,10 +32663,10 @@
         <v>2</v>
       </c>
       <c r="I6" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="J6" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -32428,10 +32692,10 @@
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="J7" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -32457,10 +32721,10 @@
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="J8" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -32474,7 +32738,7 @@
         <v>500</v>
       </c>
       <c r="D9" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E9">
         <v>13</v>
@@ -32489,10 +32753,10 @@
         <v>2</v>
       </c>
       <c r="I9" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="J9" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -32518,10 +32782,10 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="J10" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -32547,10 +32811,10 @@
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J11" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -32576,10 +32840,10 @@
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="J12" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -32605,10 +32869,10 @@
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="J13" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -32622,7 +32886,7 @@
         <v>2000</v>
       </c>
       <c r="D14" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E14">
         <v>20</v>
@@ -32637,10 +32901,10 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="J14" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -32666,10 +32930,10 @@
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="J15" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -32695,10 +32959,10 @@
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="J16" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -32724,10 +32988,10 @@
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="J17" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -32753,10 +33017,10 @@
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="J18" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -32770,7 +33034,7 @@
         <v>6000</v>
       </c>
       <c r="D19" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E19">
         <v>29</v>
@@ -32785,10 +33049,10 @@
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="J19" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -32814,10 +33078,10 @@
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="J20" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -32843,10 +33107,10 @@
         <v>2</v>
       </c>
       <c r="I21" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="J21" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -32872,10 +33136,10 @@
         <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="J22" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -32901,10 +33165,10 @@
         <v>2</v>
       </c>
       <c r="I23" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="J23" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -32918,7 +33182,7 @@
         <v>15000</v>
       </c>
       <c r="D24" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E24">
         <v>45</v>
@@ -32933,10 +33197,10 @@
         <v>3</v>
       </c>
       <c r="I24" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="J24" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -32962,10 +33226,10 @@
         <v>3</v>
       </c>
       <c r="I25" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="J25" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -32991,10 +33255,10 @@
         <v>4</v>
       </c>
       <c r="I26" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="J26" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -33020,10 +33284,10 @@
         <v>7</v>
       </c>
       <c r="I27" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="J27" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -33049,10 +33313,10 @@
         <v>8</v>
       </c>
       <c r="I28" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="J28" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -33066,7 +33330,7 @@
         <v>40000</v>
       </c>
       <c r="D29" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E29">
         <v>113</v>
@@ -33081,10 +33345,10 @@
         <v>12</v>
       </c>
       <c r="I29" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="J29" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -33095,41 +33359,41 @@
         <v>1</v>
       </c>
       <c r="D30" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="I30" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="J30" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B32" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C32">
         <v>1.3</v>
       </c>
       <c r="D32" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B34" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C34" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D34" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -33137,7 +33401,7 @@
         <v>2</v>
       </c>
       <c r="B35" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C35">
         <v>8</v>
@@ -33148,7 +33412,7 @@
         <v>3</v>
       </c>
       <c r="B36" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C36">
         <v>20</v>
@@ -33159,7 +33423,7 @@
         <v>4</v>
       </c>
       <c r="B37" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C37">
         <v>32</v>
@@ -33170,7 +33434,7 @@
         <v>5</v>
       </c>
       <c r="B38" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C38">
         <v>45</v>
@@ -33181,7 +33445,7 @@
         <v>6</v>
       </c>
       <c r="B39" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C39">
         <v>60</v>
@@ -33189,10 +33453,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B41" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C41" t="s">
         <v>31</v>
@@ -33203,58 +33467,763 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B42" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C42">
         <v>16</v>
       </c>
       <c r="D42" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B43" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C43">
         <v>1.5</v>
       </c>
       <c r="D43" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B44" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C44">
         <v>0.05</v>
       </c>
       <c r="D44" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B45" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C45">
         <v>0.15</v>
       </c>
       <c r="D45" t="s">
-        <v>392</v>
+        <v>395</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:N36"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s">
+        <v>398</v>
+      </c>
+      <c r="C4" t="s">
+        <v>313</v>
+      </c>
+      <c r="D4" t="s">
+        <v>399</v>
+      </c>
+      <c r="E4" t="s">
+        <v>400</v>
+      </c>
+      <c r="F4" t="s">
+        <v>401</v>
+      </c>
+      <c r="G4" t="s">
+        <v>402</v>
+      </c>
+      <c r="H4" t="s">
+        <v>403</v>
+      </c>
+      <c r="I4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>404</v>
+      </c>
+      <c r="B5" t="s">
+        <v>405</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>406</v>
+      </c>
+      <c r="E5">
+        <v>0.25</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="I5" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>408</v>
+      </c>
+      <c r="B6" t="s">
+        <v>409</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>410</v>
+      </c>
+      <c r="E6">
+        <v>1.2</v>
+      </c>
+      <c r="F6">
+        <v>1.08</v>
+      </c>
+      <c r="G6">
+        <v>11</v>
+      </c>
+      <c r="H6">
+        <v>1.04</v>
+      </c>
+      <c r="I6" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>412</v>
+      </c>
+      <c r="B7" t="s">
+        <v>413</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>410</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>0.9</v>
+      </c>
+      <c r="G7">
+        <v>8</v>
+      </c>
+      <c r="H7">
+        <v>1.15</v>
+      </c>
+      <c r="I7" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>415</v>
+      </c>
+      <c r="B8" t="s">
+        <v>416</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8" t="s">
+        <v>417</v>
+      </c>
+      <c r="E8">
+        <v>0.5</v>
+      </c>
+      <c r="F8">
+        <v>12.1</v>
+      </c>
+      <c r="G8">
+        <v>0.5</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>419</v>
+      </c>
+      <c r="B9" t="s">
+        <v>420</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9" t="s">
+        <v>417</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>18</v>
+      </c>
+      <c r="G9">
+        <v>0.7</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>422</v>
+      </c>
+      <c r="B10" t="s">
+        <v>423</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10" t="s">
+        <v>424</v>
+      </c>
+      <c r="E10">
+        <v>0.6</v>
+      </c>
+      <c r="F10">
+        <v>1.3</v>
+      </c>
+      <c r="G10">
+        <v>3</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>426</v>
+      </c>
+      <c r="B11" t="s">
+        <v>427</v>
+      </c>
+      <c r="C11">
+        <v>3</v>
+      </c>
+      <c r="D11" t="s">
+        <v>428</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
+      <c r="F11">
+        <v>30</v>
+      </c>
+      <c r="G11">
+        <v>12</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>430</v>
+      </c>
+      <c r="B12" t="s">
+        <v>431</v>
+      </c>
+      <c r="C12">
+        <v>3</v>
+      </c>
+      <c r="D12" t="s">
+        <v>432</v>
+      </c>
+      <c r="E12">
+        <v>0.6</v>
+      </c>
+      <c r="F12">
+        <v>3</v>
+      </c>
+      <c r="G12">
+        <v>0.15</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" t="s">
+        <v>434</v>
+      </c>
+      <c r="B13" t="s">
+        <v>435</v>
+      </c>
+      <c r="C13">
+        <v>3</v>
+      </c>
+      <c r="D13" t="s">
+        <v>436</v>
+      </c>
+      <c r="E13">
+        <v>1.5</v>
+      </c>
+      <c r="F13">
+        <v>8</v>
+      </c>
+      <c r="G13">
+        <v>0.1</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" t="s">
+        <v>438</v>
+      </c>
+      <c r="B14" t="s">
+        <v>439</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14" t="s">
+        <v>440</v>
+      </c>
+      <c r="E14">
+        <v>0.8</v>
+      </c>
+      <c r="F14">
+        <v>0.15</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
+        <v>442</v>
+      </c>
+      <c r="B15" t="s">
+        <v>443</v>
+      </c>
+      <c r="C15">
+        <v>3</v>
+      </c>
+      <c r="D15" t="s">
+        <v>440</v>
+      </c>
+      <c r="E15">
+        <v>0.5</v>
+      </c>
+      <c r="F15">
+        <v>0.2</v>
+      </c>
+      <c r="G15">
+        <v>3</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>445</v>
+      </c>
+      <c r="B16" t="s">
+        <v>446</v>
+      </c>
+      <c r="C16">
+        <v>3</v>
+      </c>
+      <c r="D16" t="s">
+        <v>440</v>
+      </c>
+      <c r="E16">
+        <v>0.6</v>
+      </c>
+      <c r="F16">
+        <v>0.15</v>
+      </c>
+      <c r="G16">
+        <v>3</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" t="s">
+        <v>448</v>
+      </c>
+      <c r="B19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" t="s">
+        <v>449</v>
+      </c>
+      <c r="B20" t="s">
+        <v>450</v>
+      </c>
+      <c r="C20">
+        <v>100</v>
+      </c>
+      <c r="D20" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" t="s">
+        <v>452</v>
+      </c>
+      <c r="B21" t="s">
+        <v>453</v>
+      </c>
+      <c r="C21">
+        <v>5</v>
+      </c>
+      <c r="D21" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" t="s">
+        <v>455</v>
+      </c>
+      <c r="B22" t="s">
+        <v>456</v>
+      </c>
+      <c r="C22">
+        <v>0.08</v>
+      </c>
+      <c r="D22" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" t="s">
+        <v>458</v>
+      </c>
+      <c r="B23" t="s">
+        <v>459</v>
+      </c>
+      <c r="C23">
+        <v>6</v>
+      </c>
+      <c r="D23" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" t="s">
+        <v>461</v>
+      </c>
+      <c r="B24" t="s">
+        <v>462</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" t="s">
+        <v>463</v>
+      </c>
+      <c r="B25" t="s">
+        <v>464</v>
+      </c>
+      <c r="C25">
+        <v>4</v>
+      </c>
+      <c r="D25" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" t="s">
+        <v>466</v>
+      </c>
+      <c r="B26" t="s">
+        <v>467</v>
+      </c>
+      <c r="C26">
+        <v>0.3</v>
+      </c>
+      <c r="D26" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" t="s">
+        <v>469</v>
+      </c>
+      <c r="B27" t="s">
+        <v>470</v>
+      </c>
+      <c r="C27">
+        <v>5</v>
+      </c>
+      <c r="D27" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" t="s">
+        <v>313</v>
+      </c>
+      <c r="B31" t="s">
+        <v>404</v>
+      </c>
+      <c r="C31" t="s">
+        <v>408</v>
+      </c>
+      <c r="D31" t="s">
+        <v>412</v>
+      </c>
+      <c r="E31" t="s">
+        <v>415</v>
+      </c>
+      <c r="F31" t="s">
+        <v>419</v>
+      </c>
+      <c r="G31" t="s">
+        <v>422</v>
+      </c>
+      <c r="H31" t="s">
+        <v>426</v>
+      </c>
+      <c r="I31" t="s">
+        <v>430</v>
+      </c>
+      <c r="J31" t="s">
+        <v>434</v>
+      </c>
+      <c r="K31" t="s">
+        <v>438</v>
+      </c>
+      <c r="L31" t="s">
+        <v>442</v>
+      </c>
+      <c r="M31" t="s">
+        <v>445</v>
+      </c>
+      <c r="N31" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32">
+        <v>1</v>
+      </c>
+      <c r="B32">
+        <v>0.45</v>
+      </c>
+      <c r="C32">
+        <v>0.35</v>
+      </c>
+      <c r="D32">
+        <v>0.2</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
+      <c r="A33">
+        <v>2</v>
+      </c>
+      <c r="B33">
+        <v>0.35</v>
+      </c>
+      <c r="C33">
+        <v>0.15</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <v>0.2</v>
+      </c>
+      <c r="F33">
+        <v>0.15</v>
+      </c>
+      <c r="G33">
+        <v>0.15</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>1</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
+      <c r="A34">
+        <v>3</v>
+      </c>
+      <c r="B34">
+        <v>0.3</v>
+      </c>
+      <c r="C34">
+        <v>0.1</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>0.1</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0.2</v>
+      </c>
+      <c r="I34">
+        <v>0.1</v>
+      </c>
+      <c r="J34">
+        <v>0.2</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0.5</v>
+      </c>
+      <c r="M34">
+        <v>0.5</v>
+      </c>
+      <c r="N34">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
+      <c r="A36" t="s">
+        <v>474</v>
       </c>
     </row>
   </sheetData>

--- a/모찌런처_밸런스시트.xlsx
+++ b/모찌런처_밸런스시트.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="485">
   <si>
     <t>모찌 런처 — 밸런스 설정값</t>
   </si>
@@ -1371,7 +1371,7 @@
     <t>볼 부풀리기 감속</t>
   </si>
   <si>
-    <t>inflate_drag_per_sec</t>
+    <t>inflate_decel_per_sec</t>
   </si>
   <si>
     <t>1/초</t>
@@ -1416,19 +1416,19 @@
     <t>퍼펙트 보너스 튀는 속도 배율 (P5)</t>
   </si>
   <si>
-    <t>홀드 판정 시간</t>
+    <t>홀드 시작 시간</t>
   </si>
   <si>
     <t>gesture_hold_sec</t>
   </si>
   <si>
-    <t>이보다 오래 누르면 볼 부풀리기, 짧게 떼면 부스터 탭</t>
+    <t>이 시간 이상 누르고 있으면 볼 부풀리기(홀드) 시작</t>
   </si>
   <si>
     <t>스와이프 거리</t>
   </si>
   <si>
-    <t>gesture_swipe_px</t>
+    <t>gesture_swipe_min_px</t>
   </si>
   <si>
     <t>아래로 이만큼 쓸면 급강하</t>
@@ -1441,6 +1441,36 @@
   </si>
   <si>
     <t>이 시간 안에 쓸어야 스와이프</t>
+  </si>
+  <si>
+    <t>부스터 Lv0 연료</t>
+  </si>
+  <si>
+    <t>boost_lv0_fuel_sec</t>
+  </si>
+  <si>
+    <t>부스터 업그레이드 Lv0 의 연료 (GDD §2: Lv0 은 연료 없음)</t>
+  </si>
+  <si>
+    <t>착지 시 분사 소멸</t>
+  </si>
+  <si>
+    <t>boost_cut_on_land</t>
+  </si>
+  <si>
+    <t>bool</t>
+  </si>
+  <si>
+    <t>TRUE 면 땅에 닿는 순간 분사 중이던 연료가 사라진다 (GDD §2)</t>
+  </si>
+  <si>
+    <t>탭 판정 시간</t>
+  </si>
+  <si>
+    <t>gesture_tap_max_sec</t>
+  </si>
+  <si>
+    <t>이 시간 이내에 손을 떼면 부스터 탭</t>
   </si>
   <si>
     <r>
@@ -4977,14 +5007,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
+      <b/>
+      <sz val="14"/>
       <name val="Arial"/>
       <charset val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="14"/>
+      <i/>
+      <sz val="11"/>
       <name val="Arial"/>
       <charset val="1"/>
     </font>
@@ -11881,7 +11911,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr defaultColWidth="8.67592592592593" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -12966,6 +12996,57 @@
       </c>
       <c r="E65" t="s">
         <v>180</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" t="s">
+        <v>181</v>
+      </c>
+      <c r="B66" t="s">
+        <v>182</v>
+      </c>
+      <c r="C66">
+        <v>0</v>
+      </c>
+      <c r="D66" t="s">
+        <v>51</v>
+      </c>
+      <c r="E66" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" t="s">
+        <v>184</v>
+      </c>
+      <c r="B67" t="s">
+        <v>185</v>
+      </c>
+      <c r="C67" t="b">
+        <v>1</v>
+      </c>
+      <c r="D67" t="s">
+        <v>186</v>
+      </c>
+      <c r="E67" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" t="s">
+        <v>188</v>
+      </c>
+      <c r="B68" t="s">
+        <v>189</v>
+      </c>
+      <c r="C68">
+        <v>0.18</v>
+      </c>
+      <c r="D68" t="s">
+        <v>51</v>
+      </c>
+      <c r="E68" t="s">
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -12990,7 +13071,7 @@
   <sheetData>
     <row r="1" ht="17.4" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -13020,40 +13101,40 @@
     </row>
     <row r="3" ht="42.6" spans="1:12">
       <c r="A3" s="4" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>27</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -17053,7 +17134,7 @@
   <sheetData>
     <row r="1" ht="17.4" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -17075,7 +17156,7 @@
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="21" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="B2" s="15"/>
       <c r="C2" s="15"/>
@@ -17117,28 +17198,28 @@
     </row>
     <row r="4" ht="28.8" spans="1:18">
       <c r="A4" s="3" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>9</v>
@@ -18308,7 +18389,7 @@
       </c>
       <c r="N28" s="15"/>
       <c r="O28" s="12" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="P28" s="15"/>
       <c r="Q28" s="15"/>
@@ -18361,13 +18442,13 @@
         <v>53</v>
       </c>
       <c r="P29" s="23" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="Q29" s="23" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="R29" s="23" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
     </row>
     <row r="30" spans="1:18">
@@ -18798,7 +18879,7 @@
       </c>
       <c r="N37" s="15"/>
       <c r="O37" s="11" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="P37" s="15"/>
       <c r="Q37" s="15"/>
@@ -31641,7 +31722,7 @@
   <sheetData>
     <row r="1" ht="17.4" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -31655,7 +31736,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>31</v>
@@ -31664,145 +31745,145 @@
         <v>32</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="7" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="B4" s="6">
         <v>10000</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="5" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="B5" s="6">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="5" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="B6" s="6">
         <v>10</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="5" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B7" s="6">
         <v>4</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="5" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="B8" s="6">
         <v>6</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="5" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="B9" s="16">
         <v>0.01</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="7" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="B10" s="16">
         <v>0.01</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="5" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="B11" s="6">
         <v>3</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="5" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="B12" s="16">
         <v>0.15</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="7" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="5" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="B13" s="6">
         <v>1380</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -31813,21 +31894,21 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="3" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="5" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="B16" s="17">
         <f>B4*B5*B6/1000</f>
@@ -31844,7 +31925,7 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="5" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="B17" s="17">
         <f>B4*(1-B9)*B7*B8/1000</f>
@@ -31861,7 +31942,7 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="7" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="B18" s="17">
         <f>B4*B10*B11*(1-B12)</f>
@@ -31878,7 +31959,7 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="12" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="B19" s="18">
         <f>SUM(B16:B18)</f>
@@ -31895,7 +31976,7 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="5" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="B20" s="19">
         <f>IF(B19&gt;0,(B16+B17)/B19,0)</f>
@@ -31906,7 +31987,7 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="7" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="B21" s="20">
         <f>IF(B4&gt;0,B19/B4,0)</f>
@@ -31923,7 +32004,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="B23" s="15"/>
       <c r="C23" s="15"/>
@@ -31951,29 +32032,29 @@
   <sheetData>
     <row r="1" ht="17.4" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="3" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="5" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="B4" s="6">
         <v>7</v>
@@ -31986,12 +32067,12 @@
         <v>210</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="5" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="B5" s="6">
         <v>7</v>
@@ -32007,7 +32088,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="7" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="B6" s="6">
         <v>1</v>
@@ -32020,12 +32101,12 @@
         <v>100</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="5" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="B7" s="6">
         <v>3</v>
@@ -32038,12 +32119,12 @@
         <v>60</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="5" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="B8" s="6">
         <v>5</v>
@@ -32056,12 +32137,12 @@
         <v>25</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="12" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="D9" s="12">
         <f>SUM(D4:D8)</f>
@@ -32070,22 +32151,22 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="3" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="5" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="B12" s="6">
         <v>100</v>
@@ -32095,12 +32176,12 @@
         <v>5.4</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="5" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="B13" s="6">
         <v>300</v>
@@ -32113,7 +32194,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="5" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="B14" s="6">
         <v>20</v>
@@ -32126,7 +32207,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="5" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="B15" s="6">
         <v>150</v>
@@ -32139,24 +32220,24 @@
     </row>
     <row r="17" ht="28.2" spans="1:5">
       <c r="A17" s="3" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="B18" s="13">
         <v>1200</v>
@@ -32175,7 +32256,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="B19" s="13">
         <v>5900</v>
@@ -32194,7 +32275,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="B20" s="13">
         <v>29000</v>
@@ -32213,7 +32294,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="B21" s="13">
         <v>5900</v>
@@ -32232,7 +32313,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="B22" s="13">
         <v>2500</v>
@@ -32251,7 +32332,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="B23" s="13">
         <v>4400</v>
@@ -32270,7 +32351,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
     </row>
   </sheetData>
@@ -32296,17 +32377,17 @@
   <sheetData>
     <row r="1" ht="17.4" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
     </row>
     <row r="4" ht="28.2" spans="1:8">
       <c r="A4" s="3" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>31</v>
@@ -32317,88 +32398,88 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="5" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="B5" s="6">
         <v>0.2</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="5" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="B6" s="6">
         <v>0.15</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="5" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="B7" s="6">
         <v>0.1</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="5" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="B8" s="6">
         <v>8</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="5" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="B9" s="6">
         <v>2</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="1:8">
       <c r="A11" s="3" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="5" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="B12" s="8">
         <v>346</v>
@@ -32428,7 +32509,7 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="5" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="B13" s="8">
         <v>1919</v>
@@ -32458,7 +32539,7 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="5" t="s">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="B14" s="8">
         <v>7903</v>
@@ -32488,7 +32569,7 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="5" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="B15" s="8">
         <v>24394</v>
@@ -32518,7 +32599,7 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="5" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="B16" s="8">
         <v>84051</v>
@@ -32548,12 +32629,12 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="2" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="11" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -32571,44 +32652,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="B4" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="C4" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="D4" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="E4" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="F4" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="G4" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="H4" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="I4" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="J4" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -32634,10 +32715,10 @@
         <v>3</v>
       </c>
       <c r="I5" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="J5" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -32663,10 +32744,10 @@
         <v>2</v>
       </c>
       <c r="I6" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="J6" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -32692,10 +32773,10 @@
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="J7" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -32721,10 +32802,10 @@
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="J8" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -32738,7 +32819,7 @@
         <v>500</v>
       </c>
       <c r="D9" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="E9">
         <v>13</v>
@@ -32753,10 +32834,10 @@
         <v>2</v>
       </c>
       <c r="I9" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="J9" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -32782,10 +32863,10 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="J10" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -32811,10 +32892,10 @@
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="J11" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -32840,10 +32921,10 @@
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="J12" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -32869,10 +32950,10 @@
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="J13" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -32886,7 +32967,7 @@
         <v>2000</v>
       </c>
       <c r="D14" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="E14">
         <v>20</v>
@@ -32901,10 +32982,10 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="J14" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -32930,10 +33011,10 @@
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="J15" t="s">
-        <v>344</v>
+        <v>354</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -32959,10 +33040,10 @@
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J16" t="s">
-        <v>346</v>
+        <v>356</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -32988,10 +33069,10 @@
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="J17" t="s">
-        <v>348</v>
+        <v>358</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -33017,10 +33098,10 @@
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="J18" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -33034,7 +33115,7 @@
         <v>6000</v>
       </c>
       <c r="D19" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="E19">
         <v>29</v>
@@ -33049,10 +33130,10 @@
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="J19" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -33078,10 +33159,10 @@
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="J20" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -33107,10 +33188,10 @@
         <v>2</v>
       </c>
       <c r="I21" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="J21" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -33136,10 +33217,10 @@
         <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="J22" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -33165,10 +33246,10 @@
         <v>2</v>
       </c>
       <c r="I23" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="J23" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -33182,7 +33263,7 @@
         <v>15000</v>
       </c>
       <c r="D24" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="E24">
         <v>45</v>
@@ -33197,10 +33278,10 @@
         <v>3</v>
       </c>
       <c r="I24" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="J24" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -33226,10 +33307,10 @@
         <v>3</v>
       </c>
       <c r="I25" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="J25" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -33255,10 +33336,10 @@
         <v>4</v>
       </c>
       <c r="I26" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="J26" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -33284,10 +33365,10 @@
         <v>7</v>
       </c>
       <c r="I27" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="J27" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -33313,10 +33394,10 @@
         <v>8</v>
       </c>
       <c r="I28" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J28" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -33330,7 +33411,7 @@
         <v>40000</v>
       </c>
       <c r="D29" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="E29">
         <v>113</v>
@@ -33345,10 +33426,10 @@
         <v>12</v>
       </c>
       <c r="I29" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="J29" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -33359,41 +33440,41 @@
         <v>1</v>
       </c>
       <c r="D30" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="I30" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="J30" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="B32" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="C32">
         <v>1.3</v>
       </c>
       <c r="D32" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="B34" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="C34" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="D34" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -33401,7 +33482,7 @@
         <v>2</v>
       </c>
       <c r="B35" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="C35">
         <v>8</v>
@@ -33412,7 +33493,7 @@
         <v>3</v>
       </c>
       <c r="B36" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="C36">
         <v>20</v>
@@ -33423,7 +33504,7 @@
         <v>4</v>
       </c>
       <c r="B37" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="C37">
         <v>32</v>
@@ -33434,7 +33515,7 @@
         <v>5</v>
       </c>
       <c r="B38" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="C38">
         <v>45</v>
@@ -33445,7 +33526,7 @@
         <v>6</v>
       </c>
       <c r="B39" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="C39">
         <v>60</v>
@@ -33453,10 +33534,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="B41" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="C41" t="s">
         <v>31</v>
@@ -33467,58 +33548,58 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="B42" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="C42">
         <v>16</v>
       </c>
       <c r="D42" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="B43" t="s">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="C43">
         <v>1.5</v>
       </c>
       <c r="D43" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="B44" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="C44">
         <v>0.05</v>
       </c>
       <c r="D44" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="B45" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="C45">
         <v>0.15</v>
       </c>
       <c r="D45" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
     </row>
   </sheetData>
@@ -33535,12 +33616,12 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -33548,25 +33629,25 @@
         <v>30</v>
       </c>
       <c r="B4" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="C4" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="D4" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="E4" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="F4" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="G4" t="s">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="H4" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="I4" t="s">
         <v>8</v>
@@ -33574,16 +33655,16 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="B5" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="E5">
         <v>0.25</v>
@@ -33592,21 +33673,21 @@
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="B6" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="E6">
         <v>1.2</v>
@@ -33621,21 +33702,21 @@
         <v>1.04</v>
       </c>
       <c r="I6" t="s">
-        <v>411</v>
+        <v>421</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="B7" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -33650,21 +33731,21 @@
         <v>1.15</v>
       </c>
       <c r="I7" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="B8" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="C8">
         <v>2</v>
       </c>
       <c r="D8" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="E8">
         <v>0.5</v>
@@ -33679,21 +33760,21 @@
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>418</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="B9" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="C9">
         <v>2</v>
       </c>
       <c r="D9" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -33708,21 +33789,21 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="B10" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="C10">
         <v>2</v>
       </c>
       <c r="D10" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="E10">
         <v>0.6</v>
@@ -33737,21 +33818,21 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="B11" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="C11">
         <v>3</v>
       </c>
       <c r="D11" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -33766,21 +33847,21 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="B12" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="C12">
         <v>3</v>
       </c>
       <c r="D12" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="E12">
         <v>0.6</v>
@@ -33795,21 +33876,21 @@
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>433</v>
+        <v>443</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="B13" t="s">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="C13">
         <v>3</v>
       </c>
       <c r="D13" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="E13">
         <v>1.5</v>
@@ -33824,21 +33905,21 @@
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="B14" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="C14">
         <v>2</v>
       </c>
       <c r="D14" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="E14">
         <v>0.8</v>
@@ -33853,21 +33934,21 @@
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="B15" t="s">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="C15">
         <v>3</v>
       </c>
       <c r="D15" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="E15">
         <v>0.5</v>
@@ -33882,21 +33963,21 @@
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="B16" t="s">
-        <v>446</v>
+        <v>456</v>
       </c>
       <c r="C16">
         <v>3</v>
       </c>
       <c r="D16" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="E16">
         <v>0.6</v>
@@ -33911,12 +33992,12 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="B19" t="s">
         <v>30</v>
@@ -33930,66 +34011,66 @@
     </row>
     <row r="20" spans="1:14">
       <c r="A20" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="B20" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="C20">
         <v>100</v>
       </c>
       <c r="D20" t="s">
-        <v>451</v>
+        <v>461</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="B21" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="C21">
         <v>5</v>
       </c>
       <c r="D21" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="B22" t="s">
-        <v>456</v>
+        <v>466</v>
       </c>
       <c r="C22">
         <v>0.08</v>
       </c>
       <c r="D22" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" t="s">
-        <v>458</v>
+        <v>468</v>
       </c>
       <c r="B23" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="C23">
         <v>6</v>
       </c>
       <c r="D23" t="s">
-        <v>460</v>
+        <v>470</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" t="s">
-        <v>461</v>
+        <v>471</v>
       </c>
       <c r="B24" t="s">
-        <v>462</v>
+        <v>472</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -34000,93 +34081,93 @@
     </row>
     <row r="25" spans="1:14">
       <c r="A25" t="s">
-        <v>463</v>
+        <v>473</v>
       </c>
       <c r="B25" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
       <c r="C25">
         <v>4</v>
       </c>
       <c r="D25" t="s">
-        <v>465</v>
+        <v>475</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" t="s">
-        <v>466</v>
+        <v>476</v>
       </c>
       <c r="B26" t="s">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="C26">
         <v>0.3</v>
       </c>
       <c r="D26" t="s">
-        <v>468</v>
+        <v>478</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" t="s">
-        <v>469</v>
+        <v>479</v>
       </c>
       <c r="B27" t="s">
-        <v>470</v>
+        <v>480</v>
       </c>
       <c r="C27">
         <v>5</v>
       </c>
       <c r="D27" t="s">
-        <v>471</v>
+        <v>481</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" t="s">
-        <v>472</v>
+        <v>482</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="B31" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="C31" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="D31" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="E31" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="F31" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="G31" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="H31" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="I31" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="J31" t="s">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="K31" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="L31" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="M31" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="N31" t="s">
-        <v>473</v>
+        <v>483</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -34223,7 +34304,7 @@
     </row>
     <row r="36" spans="1:14">
       <c r="A36" t="s">
-        <v>474</v>
+        <v>484</v>
       </c>
     </row>
   </sheetData>

--- a/모찌런처_밸런스시트.xlsx
+++ b/모찌런처_밸런스시트.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="507">
   <si>
     <t>모찌 런처 — 밸런스 설정값</t>
   </si>
@@ -1471,6 +1471,18 @@
   </si>
   <si>
     <t>이 시간 이내에 손을 떼면 부스터 탭</t>
+  </si>
+  <si>
+    <t>광고 (GDD §7 광고 배치)</t>
+  </si>
+  <si>
+    <t>결과 화면 보상형 광고 배율</t>
+  </si>
+  <si>
+    <t>ad_reward_multiplier</t>
+  </si>
+  <si>
+    <t>결과 화면 광고를 보면 그 판 씨앗 × 이 값 (GDD §2·§7 씨앗 2배)</t>
   </si>
   <si>
     <r>
@@ -4508,6 +4520,60 @@
   </si>
   <si>
     <t>최대 15%. 클리어하면 초기화</t>
+  </si>
+  <si>
+    <t>1-5 고양이 출발 지연</t>
+  </si>
+  <si>
+    <t>boss_1_5_cat_delay_sec</t>
+  </si>
+  <si>
+    <t>발사 후 고양이가 달리기 시작하는 시간(실제 초, GDD §4)</t>
+  </si>
+  <si>
+    <t>1-5 고양이 골 도달 시간</t>
+  </si>
+  <si>
+    <t>boss_1_5_cat_time_sec</t>
+  </si>
+  <si>
+    <t>발사부터 고양이가 500m 에 닿는 시간(실제 초). 속도 = 500/(이 값-지연). 1-5 클리어 수준(시뮬 13판 레벨)에서 PERFECT+부스터 3.6초는 승리, 부스터 없이 7.9초는 잡힘</t>
+  </si>
+  <si>
+    <t>2-5 분수 최소</t>
+  </si>
+  <si>
+    <t>boss_2_5_fountain_min</t>
+  </si>
+  <si>
+    <t>코스에 고정 배치하는 분수 수 최소 (GDD 2~3개)</t>
+  </si>
+  <si>
+    <t>2-5 분수 최대</t>
+  </si>
+  <si>
+    <t>boss_2_5_fountain_max</t>
+  </si>
+  <si>
+    <t>코스에 고정 배치하는 분수 수 최대</t>
+  </si>
+  <si>
+    <t>3-5 게이지 상승</t>
+  </si>
+  <si>
+    <t>boss_3_5_steal_per_sec</t>
+  </si>
+  <si>
+    <t>비행 중 까마귀 대장이 훔치는 게이지(실제 초당). 3-5 클리어 수준(29판 레벨) PERFECT+부스터 31.6초 → 약 60%, 52.6초면 100%</t>
+  </si>
+  <si>
+    <t>3-5 까마귀 충돌 게이지</t>
+  </si>
+  <si>
+    <t>boss_3_5_crow_hit_meter</t>
+  </si>
+  <si>
+    <t>까마귀에 부딪힐 때마다 게이지 추가</t>
   </si>
   <si>
     <t>오브젝트 — 효과·배치 (GDD §4 월드 테마·배치 규칙, 월드 1~3)</t>
@@ -11911,7 +11977,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr defaultColWidth="8.67592592592593" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -13047,6 +13113,40 @@
       </c>
       <c r="E68" t="s">
         <v>190</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" t="s">
+        <v>191</v>
+      </c>
+      <c r="B70" t="s">
+        <v>30</v>
+      </c>
+      <c r="C70" t="s">
+        <v>31</v>
+      </c>
+      <c r="D70" t="s">
+        <v>32</v>
+      </c>
+      <c r="E70" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" t="s">
+        <v>192</v>
+      </c>
+      <c r="B71" t="s">
+        <v>193</v>
+      </c>
+      <c r="C71">
+        <v>2</v>
+      </c>
+      <c r="D71" t="s">
+        <v>82</v>
+      </c>
+      <c r="E71" t="s">
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -13071,7 +13171,7 @@
   <sheetData>
     <row r="1" ht="17.4" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -13101,40 +13201,40 @@
     </row>
     <row r="3" ht="42.6" spans="1:12">
       <c r="A3" s="4" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>27</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -17134,7 +17234,7 @@
   <sheetData>
     <row r="1" ht="17.4" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -17156,7 +17256,7 @@
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="21" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B2" s="15"/>
       <c r="C2" s="15"/>
@@ -17198,28 +17298,28 @@
     </row>
     <row r="4" ht="28.8" spans="1:18">
       <c r="A4" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>9</v>
@@ -18389,7 +18489,7 @@
       </c>
       <c r="N28" s="15"/>
       <c r="O28" s="12" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="P28" s="15"/>
       <c r="Q28" s="15"/>
@@ -18442,13 +18542,13 @@
         <v>53</v>
       </c>
       <c r="P29" s="23" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="Q29" s="23" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="R29" s="23" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="30" spans="1:18">
@@ -18879,7 +18979,7 @@
       </c>
       <c r="N37" s="15"/>
       <c r="O37" s="11" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="P37" s="15"/>
       <c r="Q37" s="15"/>
@@ -31722,7 +31822,7 @@
   <sheetData>
     <row r="1" ht="17.4" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -31736,7 +31836,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>31</v>
@@ -31745,145 +31845,145 @@
         <v>32</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="7" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B4" s="6">
         <v>10000</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="5" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B5" s="6">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="5" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B6" s="6">
         <v>10</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="5" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B7" s="6">
         <v>4</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="5" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B8" s="6">
         <v>6</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="5" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B9" s="16">
         <v>0.01</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="7" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B10" s="16">
         <v>0.01</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="5" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B11" s="6">
         <v>3</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="5" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B12" s="16">
         <v>0.15</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="7" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="5" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B13" s="6">
         <v>1380</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -31894,21 +31994,21 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="3" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="5" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B16" s="17">
         <f>B4*B5*B6/1000</f>
@@ -31925,7 +32025,7 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="5" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B17" s="17">
         <f>B4*(1-B9)*B7*B8/1000</f>
@@ -31942,7 +32042,7 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="7" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B18" s="17">
         <f>B4*B10*B11*(1-B12)</f>
@@ -31959,7 +32059,7 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="12" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B19" s="18">
         <f>SUM(B16:B18)</f>
@@ -31976,7 +32076,7 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="5" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B20" s="19">
         <f>IF(B19&gt;0,(B16+B17)/B19,0)</f>
@@ -31987,7 +32087,7 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="7" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B21" s="20">
         <f>IF(B4&gt;0,B19/B4,0)</f>
@@ -32004,7 +32104,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B23" s="15"/>
       <c r="C23" s="15"/>
@@ -32032,29 +32132,29 @@
   <sheetData>
     <row r="1" ht="17.4" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="3" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="5" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B4" s="6">
         <v>7</v>
@@ -32067,12 +32167,12 @@
         <v>210</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="5" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B5" s="6">
         <v>7</v>
@@ -32088,7 +32188,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="7" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B6" s="6">
         <v>1</v>
@@ -32101,12 +32201,12 @@
         <v>100</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="5" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B7" s="6">
         <v>3</v>
@@ -32119,12 +32219,12 @@
         <v>60</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="5" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B8" s="6">
         <v>5</v>
@@ -32137,12 +32237,12 @@
         <v>25</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="12" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="D9" s="12">
         <f>SUM(D4:D8)</f>
@@ -32151,22 +32251,22 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="3" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="5" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B12" s="6">
         <v>100</v>
@@ -32176,12 +32276,12 @@
         <v>5.4</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="5" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B13" s="6">
         <v>300</v>
@@ -32194,7 +32294,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="5" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B14" s="6">
         <v>20</v>
@@ -32207,7 +32307,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="5" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B15" s="6">
         <v>150</v>
@@ -32220,24 +32320,24 @@
     </row>
     <row r="17" ht="28.2" spans="1:5">
       <c r="A17" s="3" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B18" s="13">
         <v>1200</v>
@@ -32256,7 +32356,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B19" s="13">
         <v>5900</v>
@@ -32275,7 +32375,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B20" s="13">
         <v>29000</v>
@@ -32294,7 +32394,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B21" s="13">
         <v>5900</v>
@@ -32313,7 +32413,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B22" s="13">
         <v>2500</v>
@@ -32332,7 +32432,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B23" s="13">
         <v>4400</v>
@@ -32351,7 +32451,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
   </sheetData>
@@ -32377,17 +32477,17 @@
   <sheetData>
     <row r="1" ht="17.4" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="4" ht="28.2" spans="1:8">
       <c r="A4" s="3" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>31</v>
@@ -32398,88 +32498,88 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="5" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B5" s="6">
         <v>0.2</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="5" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B6" s="6">
         <v>0.15</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="5" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B7" s="6">
         <v>0.1</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="5" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B8" s="6">
         <v>8</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="5" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B9" s="6">
         <v>2</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="1:8">
       <c r="A11" s="3" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="5" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B12" s="8">
         <v>346</v>
@@ -32509,7 +32609,7 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="5" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B13" s="8">
         <v>1919</v>
@@ -32539,7 +32639,7 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="5" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B14" s="8">
         <v>7903</v>
@@ -32569,7 +32669,7 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="5" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B15" s="8">
         <v>24394</v>
@@ -32599,7 +32699,7 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="5" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B16" s="8">
         <v>84051</v>
@@ -32629,12 +32729,12 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="11" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
   </sheetData>
@@ -32647,49 +32747,49 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B4" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="C4" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="D4" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="E4" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F4" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G4" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="H4" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="I4" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="J4" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -32715,10 +32815,10 @@
         <v>3</v>
       </c>
       <c r="I5" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="J5" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -32744,10 +32844,10 @@
         <v>2</v>
       </c>
       <c r="I6" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="J6" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -32773,10 +32873,10 @@
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="J7" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -32802,10 +32902,10 @@
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="J8" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -32819,7 +32919,7 @@
         <v>500</v>
       </c>
       <c r="D9" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="E9">
         <v>13</v>
@@ -32834,10 +32934,10 @@
         <v>2</v>
       </c>
       <c r="I9" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="J9" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -32863,10 +32963,10 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="J10" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -32892,10 +32992,10 @@
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="J11" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -32921,10 +33021,10 @@
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="J12" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -32950,10 +33050,10 @@
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="J13" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -32967,7 +33067,7 @@
         <v>2000</v>
       </c>
       <c r="D14" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="E14">
         <v>20</v>
@@ -32982,10 +33082,10 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="J14" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -33011,10 +33111,10 @@
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="J15" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -33040,10 +33140,10 @@
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="J16" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -33069,10 +33169,10 @@
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="J17" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -33098,10 +33198,10 @@
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="J18" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -33115,7 +33215,7 @@
         <v>6000</v>
       </c>
       <c r="D19" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="E19">
         <v>29</v>
@@ -33130,10 +33230,10 @@
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="J19" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -33159,10 +33259,10 @@
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="J20" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -33188,10 +33288,10 @@
         <v>2</v>
       </c>
       <c r="I21" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="J21" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -33217,10 +33317,10 @@
         <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="J22" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -33246,10 +33346,10 @@
         <v>2</v>
       </c>
       <c r="I23" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="J23" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -33263,7 +33363,7 @@
         <v>15000</v>
       </c>
       <c r="D24" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="E24">
         <v>45</v>
@@ -33278,10 +33378,10 @@
         <v>3</v>
       </c>
       <c r="I24" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="J24" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -33307,10 +33407,10 @@
         <v>3</v>
       </c>
       <c r="I25" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="J25" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -33336,10 +33436,10 @@
         <v>4</v>
       </c>
       <c r="I26" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="J26" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -33365,10 +33465,10 @@
         <v>7</v>
       </c>
       <c r="I27" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="J27" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -33394,10 +33494,10 @@
         <v>8</v>
       </c>
       <c r="I28" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="J28" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -33411,7 +33511,7 @@
         <v>40000</v>
       </c>
       <c r="D29" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="E29">
         <v>113</v>
@@ -33426,10 +33526,10 @@
         <v>12</v>
       </c>
       <c r="I29" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="J29" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -33440,41 +33540,41 @@
         <v>1</v>
       </c>
       <c r="D30" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="I30" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="J30" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B32" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="C32">
         <v>1.3</v>
       </c>
       <c r="D32" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B34" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="C34" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="D34" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -33482,7 +33582,7 @@
         <v>2</v>
       </c>
       <c r="B35" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="C35">
         <v>8</v>
@@ -33493,7 +33593,7 @@
         <v>3</v>
       </c>
       <c r="B36" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="C36">
         <v>20</v>
@@ -33504,7 +33604,7 @@
         <v>4</v>
       </c>
       <c r="B37" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="C37">
         <v>32</v>
@@ -33515,7 +33615,7 @@
         <v>5</v>
       </c>
       <c r="B38" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="C38">
         <v>45</v>
@@ -33526,7 +33626,7 @@
         <v>6</v>
       </c>
       <c r="B39" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="C39">
         <v>60</v>
@@ -33534,10 +33634,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
+        <v>397</v>
+      </c>
+      <c r="B41" t="s">
         <v>393</v>
-      </c>
-      <c r="B41" t="s">
-        <v>389</v>
       </c>
       <c r="C41" t="s">
         <v>31</v>
@@ -33548,58 +33648,142 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B42" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="C42">
         <v>16</v>
       </c>
       <c r="D42" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="B43" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C43">
         <v>1.5</v>
       </c>
       <c r="D43" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="B44" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="C44">
         <v>0.05</v>
       </c>
       <c r="D44" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="B45" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="C45">
         <v>0.15</v>
       </c>
       <c r="D45" t="s">
-        <v>405</v>
+        <v>409</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" t="s">
+        <v>410</v>
+      </c>
+      <c r="B46" t="s">
+        <v>411</v>
+      </c>
+      <c r="C46">
+        <v>2</v>
+      </c>
+      <c r="D46" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" t="s">
+        <v>413</v>
+      </c>
+      <c r="B47" t="s">
+        <v>414</v>
+      </c>
+      <c r="C47">
+        <v>6</v>
+      </c>
+      <c r="D47" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" t="s">
+        <v>416</v>
+      </c>
+      <c r="B48" t="s">
+        <v>417</v>
+      </c>
+      <c r="C48">
+        <v>2</v>
+      </c>
+      <c r="D48" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" t="s">
+        <v>419</v>
+      </c>
+      <c r="B49" t="s">
+        <v>420</v>
+      </c>
+      <c r="C49">
+        <v>3</v>
+      </c>
+      <c r="D49" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" t="s">
+        <v>422</v>
+      </c>
+      <c r="B50" t="s">
+        <v>423</v>
+      </c>
+      <c r="C50">
+        <v>0.019</v>
+      </c>
+      <c r="D50" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" t="s">
+        <v>425</v>
+      </c>
+      <c r="B51" t="s">
+        <v>426</v>
+      </c>
+      <c r="C51">
+        <v>0.1</v>
+      </c>
+      <c r="D51" t="s">
+        <v>427</v>
       </c>
     </row>
   </sheetData>
@@ -33616,12 +33800,12 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
-        <v>406</v>
+        <v>428</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>407</v>
+        <v>429</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -33629,25 +33813,25 @@
         <v>30</v>
       </c>
       <c r="B4" t="s">
-        <v>408</v>
+        <v>430</v>
       </c>
       <c r="C4" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="D4" t="s">
-        <v>409</v>
+        <v>431</v>
       </c>
       <c r="E4" t="s">
-        <v>410</v>
+        <v>432</v>
       </c>
       <c r="F4" t="s">
-        <v>411</v>
+        <v>433</v>
       </c>
       <c r="G4" t="s">
-        <v>412</v>
+        <v>434</v>
       </c>
       <c r="H4" t="s">
-        <v>413</v>
+        <v>435</v>
       </c>
       <c r="I4" t="s">
         <v>8</v>
@@ -33655,16 +33839,16 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="B5" t="s">
-        <v>415</v>
+        <v>437</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>416</v>
+        <v>438</v>
       </c>
       <c r="E5">
         <v>0.25</v>
@@ -33673,21 +33857,21 @@
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>417</v>
+        <v>439</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>418</v>
+        <v>440</v>
       </c>
       <c r="B6" t="s">
-        <v>419</v>
+        <v>441</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>420</v>
+        <v>442</v>
       </c>
       <c r="E6">
         <v>1.2</v>
@@ -33702,21 +33886,21 @@
         <v>1.04</v>
       </c>
       <c r="I6" t="s">
-        <v>421</v>
+        <v>443</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>422</v>
+        <v>444</v>
       </c>
       <c r="B7" t="s">
-        <v>423</v>
+        <v>445</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>420</v>
+        <v>442</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -33731,21 +33915,21 @@
         <v>1.15</v>
       </c>
       <c r="I7" t="s">
-        <v>424</v>
+        <v>446</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>425</v>
+        <v>447</v>
       </c>
       <c r="B8" t="s">
-        <v>426</v>
+        <v>448</v>
       </c>
       <c r="C8">
         <v>2</v>
       </c>
       <c r="D8" t="s">
-        <v>427</v>
+        <v>449</v>
       </c>
       <c r="E8">
         <v>0.5</v>
@@ -33760,21 +33944,21 @@
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>428</v>
+        <v>450</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>429</v>
+        <v>451</v>
       </c>
       <c r="B9" t="s">
-        <v>430</v>
+        <v>452</v>
       </c>
       <c r="C9">
         <v>2</v>
       </c>
       <c r="D9" t="s">
-        <v>427</v>
+        <v>449</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -33789,21 +33973,21 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>431</v>
+        <v>453</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>432</v>
+        <v>454</v>
       </c>
       <c r="B10" t="s">
-        <v>433</v>
+        <v>455</v>
       </c>
       <c r="C10">
         <v>2</v>
       </c>
       <c r="D10" t="s">
-        <v>434</v>
+        <v>456</v>
       </c>
       <c r="E10">
         <v>0.6</v>
@@ -33818,21 +34002,21 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>435</v>
+        <v>457</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>436</v>
+        <v>458</v>
       </c>
       <c r="B11" t="s">
-        <v>437</v>
+        <v>459</v>
       </c>
       <c r="C11">
         <v>3</v>
       </c>
       <c r="D11" t="s">
-        <v>438</v>
+        <v>460</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -33847,21 +34031,21 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>439</v>
+        <v>461</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>440</v>
+        <v>462</v>
       </c>
       <c r="B12" t="s">
-        <v>441</v>
+        <v>463</v>
       </c>
       <c r="C12">
         <v>3</v>
       </c>
       <c r="D12" t="s">
-        <v>442</v>
+        <v>464</v>
       </c>
       <c r="E12">
         <v>0.6</v>
@@ -33876,21 +34060,21 @@
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>443</v>
+        <v>465</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>444</v>
+        <v>466</v>
       </c>
       <c r="B13" t="s">
-        <v>445</v>
+        <v>467</v>
       </c>
       <c r="C13">
         <v>3</v>
       </c>
       <c r="D13" t="s">
-        <v>446</v>
+        <v>468</v>
       </c>
       <c r="E13">
         <v>1.5</v>
@@ -33905,21 +34089,21 @@
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>447</v>
+        <v>469</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>448</v>
+        <v>470</v>
       </c>
       <c r="B14" t="s">
-        <v>449</v>
+        <v>471</v>
       </c>
       <c r="C14">
         <v>2</v>
       </c>
       <c r="D14" t="s">
-        <v>450</v>
+        <v>472</v>
       </c>
       <c r="E14">
         <v>0.8</v>
@@ -33934,21 +34118,21 @@
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>451</v>
+        <v>473</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>452</v>
+        <v>474</v>
       </c>
       <c r="B15" t="s">
-        <v>453</v>
+        <v>475</v>
       </c>
       <c r="C15">
         <v>3</v>
       </c>
       <c r="D15" t="s">
-        <v>450</v>
+        <v>472</v>
       </c>
       <c r="E15">
         <v>0.5</v>
@@ -33963,21 +34147,21 @@
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>454</v>
+        <v>476</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>455</v>
+        <v>477</v>
       </c>
       <c r="B16" t="s">
-        <v>456</v>
+        <v>478</v>
       </c>
       <c r="C16">
         <v>3</v>
       </c>
       <c r="D16" t="s">
-        <v>450</v>
+        <v>472</v>
       </c>
       <c r="E16">
         <v>0.6</v>
@@ -33992,12 +34176,12 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>457</v>
+        <v>479</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>458</v>
+        <v>480</v>
       </c>
       <c r="B19" t="s">
         <v>30</v>
@@ -34011,66 +34195,66 @@
     </row>
     <row r="20" spans="1:14">
       <c r="A20" t="s">
-        <v>459</v>
+        <v>481</v>
       </c>
       <c r="B20" t="s">
-        <v>460</v>
+        <v>482</v>
       </c>
       <c r="C20">
         <v>100</v>
       </c>
       <c r="D20" t="s">
-        <v>461</v>
+        <v>483</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" t="s">
-        <v>462</v>
+        <v>484</v>
       </c>
       <c r="B21" t="s">
-        <v>463</v>
+        <v>485</v>
       </c>
       <c r="C21">
         <v>5</v>
       </c>
       <c r="D21" t="s">
-        <v>464</v>
+        <v>486</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" t="s">
-        <v>465</v>
+        <v>487</v>
       </c>
       <c r="B22" t="s">
-        <v>466</v>
+        <v>488</v>
       </c>
       <c r="C22">
         <v>0.08</v>
       </c>
       <c r="D22" t="s">
-        <v>467</v>
+        <v>489</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" t="s">
-        <v>468</v>
+        <v>490</v>
       </c>
       <c r="B23" t="s">
-        <v>469</v>
+        <v>491</v>
       </c>
       <c r="C23">
         <v>6</v>
       </c>
       <c r="D23" t="s">
-        <v>470</v>
+        <v>492</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" t="s">
-        <v>471</v>
+        <v>493</v>
       </c>
       <c r="B24" t="s">
-        <v>472</v>
+        <v>494</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -34081,93 +34265,93 @@
     </row>
     <row r="25" spans="1:14">
       <c r="A25" t="s">
-        <v>473</v>
+        <v>495</v>
       </c>
       <c r="B25" t="s">
-        <v>474</v>
+        <v>496</v>
       </c>
       <c r="C25">
         <v>4</v>
       </c>
       <c r="D25" t="s">
-        <v>475</v>
+        <v>497</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" t="s">
-        <v>476</v>
+        <v>498</v>
       </c>
       <c r="B26" t="s">
-        <v>477</v>
+        <v>499</v>
       </c>
       <c r="C26">
         <v>0.3</v>
       </c>
       <c r="D26" t="s">
-        <v>478</v>
+        <v>500</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" t="s">
-        <v>479</v>
+        <v>501</v>
       </c>
       <c r="B27" t="s">
-        <v>480</v>
+        <v>502</v>
       </c>
       <c r="C27">
         <v>5</v>
       </c>
       <c r="D27" t="s">
-        <v>481</v>
+        <v>503</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" t="s">
-        <v>482</v>
+        <v>504</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B31" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="C31" t="s">
-        <v>418</v>
+        <v>440</v>
       </c>
       <c r="D31" t="s">
-        <v>422</v>
+        <v>444</v>
       </c>
       <c r="E31" t="s">
-        <v>425</v>
+        <v>447</v>
       </c>
       <c r="F31" t="s">
-        <v>429</v>
+        <v>451</v>
       </c>
       <c r="G31" t="s">
-        <v>432</v>
+        <v>454</v>
       </c>
       <c r="H31" t="s">
-        <v>436</v>
+        <v>458</v>
       </c>
       <c r="I31" t="s">
-        <v>440</v>
+        <v>462</v>
       </c>
       <c r="J31" t="s">
-        <v>444</v>
+        <v>466</v>
       </c>
       <c r="K31" t="s">
-        <v>448</v>
+        <v>470</v>
       </c>
       <c r="L31" t="s">
-        <v>452</v>
+        <v>474</v>
       </c>
       <c r="M31" t="s">
-        <v>455</v>
+        <v>477</v>
       </c>
       <c r="N31" t="s">
-        <v>483</v>
+        <v>505</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -34304,7 +34488,7 @@
     </row>
     <row r="36" spans="1:14">
       <c r="A36" t="s">
-        <v>484</v>
+        <v>506</v>
       </c>
     </row>
   </sheetData>

--- a/모찌런처_밸런스시트.xlsx
+++ b/모찌런처_밸런스시트.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="511">
   <si>
     <t>모찌 런처 — 밸런스 설정값</t>
   </si>
@@ -1483,6 +1483,18 @@
   </si>
   <si>
     <t>결과 화면 광고를 보면 그 판 씨앗 × 이 값 (GDD §2·§7 씨앗 2배)</t>
+  </si>
+  <si>
+    <t>렌더링 (GDD §3 성능)</t>
+  </si>
+  <si>
+    <t>저사양 모드 기본값</t>
+  </si>
+  <si>
+    <t>render_low_spec</t>
+  </si>
+  <si>
+    <t>TRUE 면 털 질감·배경 흐림(대기 원근 안개·해 글로우)을 끈다. 기기 설정으로 덮어씀 (P9 이후)</t>
   </si>
   <si>
     <r>
@@ -11977,7 +11989,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr defaultColWidth="8.67592592592593" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -13147,6 +13159,40 @@
       </c>
       <c r="E71" t="s">
         <v>194</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" t="s">
+        <v>195</v>
+      </c>
+      <c r="B73" t="s">
+        <v>30</v>
+      </c>
+      <c r="C73" t="s">
+        <v>31</v>
+      </c>
+      <c r="D73" t="s">
+        <v>32</v>
+      </c>
+      <c r="E73" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" t="s">
+        <v>196</v>
+      </c>
+      <c r="B74" t="s">
+        <v>197</v>
+      </c>
+      <c r="C74" t="b">
+        <v>0</v>
+      </c>
+      <c r="D74" t="s">
+        <v>186</v>
+      </c>
+      <c r="E74" t="s">
+        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -13171,7 +13217,7 @@
   <sheetData>
     <row r="1" ht="17.4" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -13201,40 +13247,40 @@
     </row>
     <row r="3" ht="42.6" spans="1:12">
       <c r="A3" s="4" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>27</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -17234,7 +17280,7 @@
   <sheetData>
     <row r="1" ht="17.4" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -17256,7 +17302,7 @@
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="21" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B2" s="15"/>
       <c r="C2" s="15"/>
@@ -17298,28 +17344,28 @@
     </row>
     <row r="4" ht="28.8" spans="1:18">
       <c r="A4" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>9</v>
@@ -18489,7 +18535,7 @@
       </c>
       <c r="N28" s="15"/>
       <c r="O28" s="12" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="P28" s="15"/>
       <c r="Q28" s="15"/>
@@ -18542,13 +18588,13 @@
         <v>53</v>
       </c>
       <c r="P29" s="23" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="Q29" s="23" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="R29" s="23" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="30" spans="1:18">
@@ -18979,7 +19025,7 @@
       </c>
       <c r="N37" s="15"/>
       <c r="O37" s="11" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="P37" s="15"/>
       <c r="Q37" s="15"/>
@@ -31822,7 +31868,7 @@
   <sheetData>
     <row r="1" ht="17.4" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -31836,7 +31882,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>31</v>
@@ -31845,145 +31891,145 @@
         <v>32</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="7" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B4" s="6">
         <v>10000</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="5" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B5" s="6">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="5" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B6" s="6">
         <v>10</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="5" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B7" s="6">
         <v>4</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="5" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B8" s="6">
         <v>6</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="5" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B9" s="16">
         <v>0.01</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="7" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B10" s="16">
         <v>0.01</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="5" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B11" s="6">
         <v>3</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="5" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B12" s="16">
         <v>0.15</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="7" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="5" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B13" s="6">
         <v>1380</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -31994,21 +32040,21 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="3" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="5" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B16" s="17">
         <f>B4*B5*B6/1000</f>
@@ -32025,7 +32071,7 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="5" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B17" s="17">
         <f>B4*(1-B9)*B7*B8/1000</f>
@@ -32042,7 +32088,7 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="7" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B18" s="17">
         <f>B4*B10*B11*(1-B12)</f>
@@ -32059,7 +32105,7 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="12" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B19" s="18">
         <f>SUM(B16:B18)</f>
@@ -32076,7 +32122,7 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B20" s="19">
         <f>IF(B19&gt;0,(B16+B17)/B19,0)</f>
@@ -32087,7 +32133,7 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="7" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B21" s="20">
         <f>IF(B4&gt;0,B19/B4,0)</f>
@@ -32104,7 +32150,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B23" s="15"/>
       <c r="C23" s="15"/>
@@ -32132,29 +32178,29 @@
   <sheetData>
     <row r="1" ht="17.4" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="3" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B4" s="6">
         <v>7</v>
@@ -32167,12 +32213,12 @@
         <v>210</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="5" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B5" s="6">
         <v>7</v>
@@ -32188,7 +32234,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="7" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B6" s="6">
         <v>1</v>
@@ -32201,12 +32247,12 @@
         <v>100</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="5" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B7" s="6">
         <v>3</v>
@@ -32219,12 +32265,12 @@
         <v>60</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="5" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B8" s="6">
         <v>5</v>
@@ -32237,12 +32283,12 @@
         <v>25</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="12" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D9" s="12">
         <f>SUM(D4:D8)</f>
@@ -32251,22 +32297,22 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="3" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="5" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B12" s="6">
         <v>100</v>
@@ -32276,12 +32322,12 @@
         <v>5.4</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="5" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B13" s="6">
         <v>300</v>
@@ -32294,7 +32340,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="5" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B14" s="6">
         <v>20</v>
@@ -32307,7 +32353,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B15" s="6">
         <v>150</v>
@@ -32320,24 +32366,24 @@
     </row>
     <row r="17" ht="28.2" spans="1:5">
       <c r="A17" s="3" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B18" s="13">
         <v>1200</v>
@@ -32356,7 +32402,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B19" s="13">
         <v>5900</v>
@@ -32375,7 +32421,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B20" s="13">
         <v>29000</v>
@@ -32394,7 +32440,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B21" s="13">
         <v>5900</v>
@@ -32413,7 +32459,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B22" s="13">
         <v>2500</v>
@@ -32432,7 +32478,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B23" s="13">
         <v>4400</v>
@@ -32451,7 +32497,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -32477,17 +32523,17 @@
   <sheetData>
     <row r="1" ht="17.4" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="4" ht="28.2" spans="1:8">
       <c r="A4" s="3" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>31</v>
@@ -32498,88 +32544,88 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="5" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B5" s="6">
         <v>0.2</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="5" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B6" s="6">
         <v>0.15</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="5" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B7" s="6">
         <v>0.1</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="5" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B8" s="6">
         <v>8</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="5" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B9" s="6">
         <v>2</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="1:8">
       <c r="A11" s="3" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="5" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B12" s="8">
         <v>346</v>
@@ -32609,7 +32655,7 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="5" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B13" s="8">
         <v>1919</v>
@@ -32639,7 +32685,7 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B14" s="8">
         <v>7903</v>
@@ -32669,7 +32715,7 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="5" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B15" s="8">
         <v>24394</v>
@@ -32699,7 +32745,7 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="5" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B16" s="8">
         <v>84051</v>
@@ -32729,12 +32775,12 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="2" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="11" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
   </sheetData>
@@ -32752,44 +32798,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B4" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C4" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="D4" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E4" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F4" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="G4" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="H4" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="I4" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="J4" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -32815,10 +32861,10 @@
         <v>3</v>
       </c>
       <c r="I5" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="J5" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -32844,10 +32890,10 @@
         <v>2</v>
       </c>
       <c r="I6" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="J6" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -32873,10 +32919,10 @@
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="J7" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -32902,10 +32948,10 @@
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="J8" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -32919,7 +32965,7 @@
         <v>500</v>
       </c>
       <c r="D9" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E9">
         <v>13</v>
@@ -32934,10 +32980,10 @@
         <v>2</v>
       </c>
       <c r="I9" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="J9" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -32963,10 +33009,10 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="J10" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -32992,10 +33038,10 @@
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="J11" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -33021,10 +33067,10 @@
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="J12" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -33050,10 +33096,10 @@
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="J13" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -33067,7 +33113,7 @@
         <v>2000</v>
       </c>
       <c r="D14" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E14">
         <v>20</v>
@@ -33082,10 +33128,10 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="J14" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -33111,10 +33157,10 @@
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="J15" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -33140,10 +33186,10 @@
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="J16" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -33169,10 +33215,10 @@
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="J17" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -33198,10 +33244,10 @@
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="J18" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -33215,7 +33261,7 @@
         <v>6000</v>
       </c>
       <c r="D19" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E19">
         <v>29</v>
@@ -33230,10 +33276,10 @@
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="J19" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -33259,10 +33305,10 @@
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="J20" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -33288,10 +33334,10 @@
         <v>2</v>
       </c>
       <c r="I21" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="J21" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -33317,10 +33363,10 @@
         <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="J22" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -33346,10 +33392,10 @@
         <v>2</v>
       </c>
       <c r="I23" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="J23" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -33363,7 +33409,7 @@
         <v>15000</v>
       </c>
       <c r="D24" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E24">
         <v>45</v>
@@ -33378,10 +33424,10 @@
         <v>3</v>
       </c>
       <c r="I24" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="J24" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -33407,10 +33453,10 @@
         <v>3</v>
       </c>
       <c r="I25" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="J25" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -33436,10 +33482,10 @@
         <v>4</v>
       </c>
       <c r="I26" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="J26" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -33465,10 +33511,10 @@
         <v>7</v>
       </c>
       <c r="I27" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="J27" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -33494,10 +33540,10 @@
         <v>8</v>
       </c>
       <c r="I28" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="J28" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -33511,7 +33557,7 @@
         <v>40000</v>
       </c>
       <c r="D29" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E29">
         <v>113</v>
@@ -33526,10 +33572,10 @@
         <v>12</v>
       </c>
       <c r="I29" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="J29" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -33540,41 +33586,41 @@
         <v>1</v>
       </c>
       <c r="D30" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="I30" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="J30" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B32" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C32">
         <v>1.3</v>
       </c>
       <c r="D32" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="B34" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C34" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="D34" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -33582,7 +33628,7 @@
         <v>2</v>
       </c>
       <c r="B35" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="C35">
         <v>8</v>
@@ -33593,7 +33639,7 @@
         <v>3</v>
       </c>
       <c r="B36" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="C36">
         <v>20</v>
@@ -33604,7 +33650,7 @@
         <v>4</v>
       </c>
       <c r="B37" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="C37">
         <v>32</v>
@@ -33615,7 +33661,7 @@
         <v>5</v>
       </c>
       <c r="B38" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="C38">
         <v>45</v>
@@ -33626,7 +33672,7 @@
         <v>6</v>
       </c>
       <c r="B39" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="C39">
         <v>60</v>
@@ -33634,10 +33680,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
+        <v>401</v>
+      </c>
+      <c r="B41" t="s">
         <v>397</v>
-      </c>
-      <c r="B41" t="s">
-        <v>393</v>
       </c>
       <c r="C41" t="s">
         <v>31</v>
@@ -33648,142 +33694,142 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="B42" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="C42">
         <v>16</v>
       </c>
       <c r="D42" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B43" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="C43">
         <v>1.5</v>
       </c>
       <c r="D43" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="B44" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="C44">
         <v>0.05</v>
       </c>
       <c r="D44" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="B45" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C45">
         <v>0.15</v>
       </c>
       <c r="D45" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B46" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="C46">
         <v>2</v>
       </c>
       <c r="D46" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="B47" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C47">
         <v>6</v>
       </c>
       <c r="D47" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="B48" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="C48">
         <v>2</v>
       </c>
       <c r="D48" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="B49" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="C49">
         <v>3</v>
       </c>
       <c r="D49" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B50" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C50">
         <v>0.019</v>
       </c>
       <c r="D50" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="B51" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="C51">
         <v>0.1</v>
       </c>
       <c r="D51" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
   </sheetData>
@@ -33800,12 +33846,12 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -33813,25 +33859,25 @@
         <v>30</v>
       </c>
       <c r="B4" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C4" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D4" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="E4" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="F4" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="G4" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="H4" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="I4" t="s">
         <v>8</v>
@@ -33839,16 +33885,16 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="B5" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="E5">
         <v>0.25</v>
@@ -33857,21 +33903,21 @@
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="B6" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="E6">
         <v>1.2</v>
@@ -33886,21 +33932,21 @@
         <v>1.04</v>
       </c>
       <c r="I6" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="B7" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -33915,21 +33961,21 @@
         <v>1.15</v>
       </c>
       <c r="I7" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="B8" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="C8">
         <v>2</v>
       </c>
       <c r="D8" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="E8">
         <v>0.5</v>
@@ -33944,21 +33990,21 @@
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="B9" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="C9">
         <v>2</v>
       </c>
       <c r="D9" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -33973,21 +34019,21 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="B10" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="C10">
         <v>2</v>
       </c>
       <c r="D10" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="E10">
         <v>0.6</v>
@@ -34002,21 +34048,21 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="B11" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="C11">
         <v>3</v>
       </c>
       <c r="D11" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -34031,21 +34077,21 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="B12" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="C12">
         <v>3</v>
       </c>
       <c r="D12" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="E12">
         <v>0.6</v>
@@ -34060,21 +34106,21 @@
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="B13" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="C13">
         <v>3</v>
       </c>
       <c r="D13" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="E13">
         <v>1.5</v>
@@ -34089,21 +34135,21 @@
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="B14" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C14">
         <v>2</v>
       </c>
       <c r="D14" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="E14">
         <v>0.8</v>
@@ -34118,21 +34164,21 @@
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="B15" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="C15">
         <v>3</v>
       </c>
       <c r="D15" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="E15">
         <v>0.5</v>
@@ -34147,21 +34193,21 @@
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="B16" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="C16">
         <v>3</v>
       </c>
       <c r="D16" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="E16">
         <v>0.6</v>
@@ -34176,12 +34222,12 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="B19" t="s">
         <v>30</v>
@@ -34195,66 +34241,66 @@
     </row>
     <row r="20" spans="1:14">
       <c r="A20" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="B20" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="C20">
         <v>100</v>
       </c>
       <c r="D20" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="B21" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="C21">
         <v>5</v>
       </c>
       <c r="D21" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="B22" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="C22">
         <v>0.08</v>
       </c>
       <c r="D22" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="B23" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="C23">
         <v>6</v>
       </c>
       <c r="D23" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="B24" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -34265,93 +34311,93 @@
     </row>
     <row r="25" spans="1:14">
       <c r="A25" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="B25" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="C25">
         <v>4</v>
       </c>
       <c r="D25" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="B26" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="C26">
         <v>0.3</v>
       </c>
       <c r="D26" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="B27" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="C27">
         <v>5</v>
       </c>
       <c r="D27" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B31" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="C31" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="D31" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="E31" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="F31" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="G31" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="H31" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="I31" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="J31" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="K31" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="L31" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="M31" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="N31" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -34488,7 +34534,7 @@
     </row>
     <row r="36" spans="1:14">
       <c r="A36" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
   </sheetData>
